--- a/examples/00981_中芯国际_估值模型.xlsx
+++ b/examples/00981_中芯国际_估值模型.xlsx
@@ -39,8 +39,8 @@
     <definedName name="PAYOUT_Y1">Assumptions!$C$53</definedName>
     <definedName name="MIN_CASH_PCT">Assumptions!$C$57</definedName>
     <definedName name="SHARES_DIL">Equity_Roll!$C$21</definedName>
-    <definedName name="DCF_PS">DCF!$D$25</definedName>
-    <definedName name="FCFE_PS">FCFE!$D$18</definedName>
+    <definedName name="DCF_PS">DCF!$D$26</definedName>
+    <definedName name="FCFE_PS">FCFE!$D$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="1000" iterateDelta="0.0001"/>
 </workbook>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="C22" s="4">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
     </row>
@@ -953,7 +953,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>5. DCF年中折现: 估值基准日2026-08-17, t=0.5/1.5/.../4.5; EV→Equity桥含货币资金/交易性金融资产/其他权益工具投资/有息负债;</t>
+          <t>5. DCF年中折现: 估值基准日2026-08-17, t=0.5/1.5/.../4.5; EV→Equity桥含货币资金/交易性金融资产/其他权益工具投资/有息负债/少数股东权益;</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>31.9</v>
@@ -4824,7 +4824,7 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>0</v>
+        <v>14117.1</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>14266.4</v>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>5746.7</v>
+        <v>15020.6</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>-0.1</v>
@@ -5174,7 +5174,7 @@
         </is>
       </c>
       <c r="B15" s="25" t="n">
-        <v>0</v>
+        <v>10729.5</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>11255.8</v>
@@ -5314,7 +5314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5778,101 +5778,117 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>减: 少数股东权益(2025A末)</t>
+        </is>
+      </c>
+      <c r="D23" s="26">
+        <f>-BS!D44</f>
+        <v/>
+      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>EV桥得归母口径股权价值须扣少数股东权益(账面值); 无少数股东权益的标的为0, 不影响结果</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>净现金调整合计</t>
         </is>
       </c>
-      <c r="D23" s="26">
-        <f>D19+D20+D21+D22</f>
-        <v/>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="D24" s="26">
+        <f>D19+D20+D21+D22+D23</f>
+        <v/>
+      </c>
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>供Sensitivity/Scenarios页引用</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>股权价值</t>
-        </is>
-      </c>
-      <c r="D24" s="36">
-        <f>D18+D23</f>
-        <v/>
-      </c>
-      <c r="J24" s="11" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>股权价值</t>
+        </is>
+      </c>
+      <c r="D25" s="36">
+        <f>D18+D24</f>
+        <v/>
+      </c>
+      <c r="J25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
           <t>每股价值 (元)</t>
         </is>
       </c>
-      <c r="D25" s="15">
-        <f>D24/Equity_Roll!$C$21</f>
-        <v/>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="D26" s="15">
+        <f>D25/Equity_Roll!$C$21</f>
+        <v/>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
         <is>
           <t>＝股权价值/稀释股数(Equity_Roll页)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>现价 (2026-08-17)</t>
         </is>
       </c>
-      <c r="D26" s="14">
+      <c r="D27" s="14">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="J26" s="11" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="J27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>隐含涨跌幅</t>
         </is>
       </c>
-      <c r="D27" s="43">
-        <f>D25/D26-1</f>
-        <v/>
-      </c>
-      <c r="J27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>隐含2026E P/E</t>
-        </is>
-      </c>
-      <c r="D28" s="44">
-        <f>D24/IS!E20</f>
-        <v/>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>＝股权价值/2026E归母</t>
-        </is>
-      </c>
+      <c r="D28" s="43">
+        <f>D26/D27-1</f>
+        <v/>
+      </c>
+      <c r="J28" s="11" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>隐含2026E P/E</t>
+        </is>
+      </c>
+      <c r="D29" s="44">
+        <f>D25/IS!E20</f>
+        <v/>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>＝股权价值/2026E归母</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
           <t>隐含2026E EV/EBITDA</t>
         </is>
       </c>
-      <c r="D29" s="44">
+      <c r="D30" s="44">
         <f>D18/(IS!E23+PPE!E19)</f>
         <v/>
       </c>
-      <c r="J29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="J30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>注: 估值基准日2026-08-17, 与2026财年现金流起点存在时间错位; 年中折现(t=0.5起)为该错位的标准近似处理, 不再单独做stub调整</t>
         </is>
@@ -5881,7 +5897,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5894,7 +5910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5919,7 +5935,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>单位: 美元百万元(财报口径) | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得股权价值, 无需EV→Equity桥</t>
+          <t>单位: 美元百万元(财报口径) | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按g封顶)</t>
         </is>
       </c>
     </row>
@@ -6121,248 +6137,296 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>理财净变动(勾稽参考, 不计入FCFE)</t>
+        </is>
+      </c>
+      <c r="E9" s="26">
+        <f>-FIN!E62</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>-FIN!F62</f>
+        <v/>
+      </c>
+      <c r="G9" s="26">
+        <f>-FIN!G62</f>
+        <v/>
+      </c>
+      <c r="H9" s="26">
+        <f>-FIN!H62</f>
+        <v/>
+      </c>
+      <c r="I9" s="26">
+        <f>-FIN!I62</f>
+        <v/>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>＝-FIN理财净变动: sweep溢出购买理财为现金↔理财的形态转换(资产仍在表内归属股东), 故不计入FCFE; 显性列示供FCFE↔FCFF差异勾稽(FCFF也未扣理财购买, 两法在此口径一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>FCFE</t>
         </is>
       </c>
-      <c r="E9" s="36">
+      <c r="E10" s="36">
         <f>E4+E5-E6-E7+E8</f>
         <v/>
       </c>
-      <c r="F9" s="36">
+      <c r="F10" s="36">
         <f>F4+F5-F6-F7+F8</f>
         <v/>
       </c>
-      <c r="G9" s="36">
+      <c r="G10" s="36">
         <f>G4+G5-G6-G7+G8</f>
         <v/>
       </c>
-      <c r="H9" s="36">
+      <c r="H10" s="36">
         <f>H4+H5-H6-H7+H8</f>
         <v/>
       </c>
-      <c r="I9" s="36">
+      <c r="I10" s="36">
         <f>I4+I5-I6-I7+I8</f>
         <v/>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>＝归母+D&amp;A-ΔNWC-Capex+净新增借款</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>折现年序(年中)</t>
-        </is>
-      </c>
-      <c r="E10" s="42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G10" s="42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>年中折现, 与DCF页同口径</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>折现因子 (Ke)</t>
-        </is>
-      </c>
-      <c r="E11" s="32">
-        <f>1/(1+KE)^E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="32">
-        <f>1/(1+KE)^F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="32">
-        <f>1/(1+KE)^G10</f>
-        <v/>
-      </c>
-      <c r="H11" s="32">
-        <f>1/(1+KE)^H10</f>
-        <v/>
-      </c>
-      <c r="I11" s="32">
-        <f>1/(1+KE)^I10</f>
-        <v/>
+          <t>折现年序(年中)</t>
+        </is>
+      </c>
+      <c r="E11" s="42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" s="42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="42" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I11" s="42" t="n">
+        <v>4.5</v>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>＝1/(1+Ke)^t; Ke为named range(Assumptions股权成本)</t>
+          <t>年中折现, 与DCF页同口径</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>折现因子 (Ke)</t>
+        </is>
+      </c>
+      <c r="E12" s="32">
+        <f>1/(1+KE)^E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="32">
+        <f>1/(1+KE)^F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="32">
+        <f>1/(1+KE)^G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="32">
+        <f>1/(1+KE)^H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="32">
+        <f>1/(1+KE)^I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>＝1/(1+Ke)^t; Ke为named range(Assumptions股权成本)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>PV(FCFE)</t>
         </is>
       </c>
-      <c r="E12" s="26">
-        <f>E9*E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="26">
-        <f>F9*F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="26">
-        <f>G9*G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="26">
-        <f>H9*H11</f>
-        <v/>
-      </c>
-      <c r="I12" s="26">
-        <f>I9*I11</f>
-        <v/>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="E13" s="26">
+        <f>E10*E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="26">
+        <f>F10*F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="26">
+        <f>G10*G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="26">
+        <f>H10*H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="26">
+        <f>I10*I12</f>
+        <v/>
+      </c>
+      <c r="J13" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>显性期PV合计 (2026-2030)</t>
         </is>
       </c>
-      <c r="D14" s="36">
-        <f>SUM(E12:I12)</f>
-        <v/>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>终值 TV (Gordon)</t>
-        </is>
-      </c>
-      <c r="D15" s="26">
-        <f>I9*(1+TERM_G)/(KE-TERM_G)</f>
-        <v/>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>＝FCFE2030×(1+g)/(Ke-g); Ke/g均为named range</t>
-        </is>
-      </c>
+      <c r="D15" s="36">
+        <f>SUM(E13:I13)</f>
+        <v/>
+      </c>
+      <c r="J15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>正常化FCFE (2030E, 终值口径)</t>
+        </is>
+      </c>
+      <c r="D16" s="26">
+        <f>I10-I8+MIN(I8,FIN!I56*TERM_G)</f>
+        <v/>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
+          <t>净新增借款按g封顶: 终值内净新增借款取MIN(实际调度, 2030E期末有息负债×g), 防止显性期末大额净融资被Gordon公式永续外推; 去杠杆/平稳年(实际≤封顶值)维持实际调度不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>终值 TV (Gordon, 正常化FCFE)</t>
+        </is>
+      </c>
+      <c r="D17" s="26">
+        <f>D16*(1+TERM_G)/(KE-TERM_G)</f>
+        <v/>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>＝正常化FCFE2030×(1+g)/(Ke-g); Ke/g均为named range</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>PV(终值)</t>
         </is>
       </c>
-      <c r="D16" s="26">
-        <f>D15*I11</f>
-        <v/>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="D18" s="26">
+        <f>D17*I12</f>
+        <v/>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>终值按t=4.5折现(与DCF页一致)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>股权价值 (FCFE口径)</t>
         </is>
       </c>
-      <c r="D17" s="36">
-        <f>D14+D16</f>
-        <v/>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="D19" s="36">
+        <f>D15+D18</f>
+        <v/>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>FCFE直接折现为股权价值, 无需净现金桥</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>每股价值 (元)</t>
-        </is>
-      </c>
-      <c r="D18" s="15">
-        <f>D17/SHARES_DIL</f>
-        <v/>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>＝股权价值/稀释股数(named range)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>对照: FCFF口径每股价值 (元)</t>
-        </is>
-      </c>
-      <c r="D19" s="14">
-        <f>DCF!D25</f>
-        <v/>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>＝DCF页主输出</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D20" s="15">
+        <f>D19/SHARES_DIL</f>
+        <v/>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>＝股权价值/稀释股数(named range)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>对照: FCFF口径每股价值 (元)</t>
+        </is>
+      </c>
+      <c r="D21" s="14">
+        <f>DCF!D26</f>
+        <v/>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>＝DCF页主输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
           <t>两法差异 (FCFE/FCFF-1)</t>
         </is>
       </c>
-      <c r="D20" s="43">
-        <f>D18/D19-1</f>
-        <v/>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="D22" s="43">
+        <f>D20/D21-1</f>
+        <v/>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve"> Checks页含一致性信息行</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>两法差异原因</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>①折现率不同: FCFF按WACC(全资本成本, 税盾在分母)折现, FCFE按Ke(纯股权成本)折现; ②口径不同: FCFF为企业自由现金流, 须经EV→Equity桥加回净现金/扣有息负债, FCFE已含净新增借款、直接对应股权; ③杠杆路径不同: FCFE逐年反映FIN页revolver/sweep实际债务调度(资本结构动态变化), FCFF隐含目标结构(Wd)恒定; ④两法在"恒定资本结构+一致税盾处理"下理论等价, 实务差异主要来自债务调度时点、净现金桥与折现率差; 差异幅度大时应复查融资假设</t>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>①折现率不同: FCFF按WACC(全资本成本, 税盾在分母)折现, FCFE按Ke(纯股权成本)折现; ②口径不同: FCFF为企业自由现金流, 须经EV→Equity桥加回净现金/扣有息负债/扣少数股东权益, FCFE基于归母净利折现、直接对应归母股权价值, 少数股东权益已在DCF页EV→Equity桥扣除, 本页无需再扣; ③杠杆路径不同: FCFE逐年反映FIN页revolver/sweep实际债务调度(资本结构动态变化), FCFF隐含目标结构(Wd)恒定; ④理财净变动(上行勾稽参考行)为现金形态转换, 两法均未计入, 不构成差异来源; ⑤两法在"恒定资本结构+一致税盾处理"下理论等价, 实务差异主要来自债务调度时点、净现金桥与折现率差; 差异幅度大时应复查融资假设</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="B23:J23"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B21:J21"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6514,7 +6578,7 @@
         <v/>
       </c>
       <c r="D6" s="45" t="n">
-        <v>120.51</v>
+        <v>121.07</v>
       </c>
       <c r="E6" s="26">
         <f>Assumptions!$C$13/100</f>
@@ -6632,7 +6696,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>相对现价9.6218元空间</t>
+          <t>相对现价9.6667元空间</t>
         </is>
       </c>
       <c r="C15" s="16">
@@ -6727,23 +6791,23 @@
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+C$5)/($B6-C$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+C$5)/($B6-C$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+D$5)/($B6-D$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+D$5)/($B6-D$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+E$5)/($B6-E$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+E$5)/($B6-E$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+F$5)/($B6-F$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+F$5)/($B6-F$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+G$5)/($B6-G$5)/(1+$B6)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B6)^0.5+DCF!$F$10/(1+$B6)^1.5+DCF!$G$10/(1+$B6)^2.5+DCF!$H$10/(1+$B6)^3.5+DCF!$I$10/(1+$B6)^4.5+DCF!$I$10*(1+G$5)/($B6-G$5)/(1+$B6)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -6753,23 +6817,23 @@
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+C$5)/($B7-C$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+C$5)/($B7-C$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+D$5)/($B7-D$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+D$5)/($B7-D$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+E$5)/($B7-E$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+E$5)/($B7-E$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+F$5)/($B7-F$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+F$5)/($B7-F$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+G$5)/($B7-G$5)/(1+$B7)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B7)^0.5+DCF!$F$10/(1+$B7)^1.5+DCF!$G$10/(1+$B7)^2.5+DCF!$H$10/(1+$B7)^3.5+DCF!$I$10/(1+$B7)^4.5+DCF!$I$10*(1+G$5)/($B7-G$5)/(1+$B7)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -6779,23 +6843,23 @@
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+C$5)/($B8-C$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+C$5)/($B8-C$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+D$5)/($B8-D$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+D$5)/($B8-D$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E8" s="48">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+E$5)/($B8-E$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+E$5)/($B8-E$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+F$5)/($B8-F$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+F$5)/($B8-F$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+G$5)/($B8-G$5)/(1+$B8)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B8)^0.5+DCF!$F$10/(1+$B8)^1.5+DCF!$G$10/(1+$B8)^2.5+DCF!$H$10/(1+$B8)^3.5+DCF!$I$10/(1+$B8)^4.5+DCF!$I$10*(1+G$5)/($B8-G$5)/(1+$B8)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -6805,23 +6869,23 @@
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+C$5)/($B9-C$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+C$5)/($B9-C$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+D$5)/($B9-D$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+D$5)/($B9-D$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+E$5)/($B9-E$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+E$5)/($B9-E$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+F$5)/($B9-F$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+F$5)/($B9-F$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+G$5)/($B9-G$5)/(1+$B9)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B9)^0.5+DCF!$F$10/(1+$B9)^1.5+DCF!$G$10/(1+$B9)^2.5+DCF!$H$10/(1+$B9)^3.5+DCF!$I$10/(1+$B9)^4.5+DCF!$I$10*(1+G$5)/($B9-G$5)/(1+$B9)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -6831,23 +6895,23 @@
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+C$5)/($B10-C$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+C$5)/($B10-C$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+D$5)/($B10-D$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+D$5)/($B10-D$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+E$5)/($B10-E$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+E$5)/($B10-E$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+F$5)/($B10-F$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+F$5)/($B10-F$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+G$5)/($B10-G$5)/(1+$B10)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(DCF!$E$10/(1+$B10)^0.5+DCF!$F$10/(1+$B10)^1.5+DCF!$G$10/(1+$B10)^2.5+DCF!$H$10/(1+$B10)^3.5+DCF!$I$10/(1+$B10)^4.5+DCF!$I$10*(1+G$5)/($B10-G$5)/(1+$B10)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
     </row>
@@ -7105,11 +7169,11 @@
         <v>-40</v>
       </c>
       <c r="C25" s="14">
-        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>C25/DCF!$D$25-1</f>
+        <f>C25/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7118,11 +7182,11 @@
         <v>-20</v>
       </c>
       <c r="C26" s="14">
-        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>C26/DCF!$D$25-1</f>
+        <f>C26/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7131,11 +7195,11 @@
         <v>0</v>
       </c>
       <c r="C27" s="48">
-        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>C27/DCF!$D$25-1</f>
+        <f>C27/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7144,11 +7208,11 @@
         <v>20</v>
       </c>
       <c r="C28" s="14">
-        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>C28/DCF!$D$25-1</f>
+        <f>C28/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7157,11 +7221,11 @@
         <v>40</v>
       </c>
       <c r="C29" s="14">
-        <f>((DCF!E$10+$B29/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B29/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B29/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B29/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B29/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B29/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B29/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B29/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B29/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B29/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B29/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B29/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>C29/DCF!$D$25-1</f>
+        <f>C29/DCF!$D$26-1</f>
         <v/>
       </c>
     </row>
@@ -7409,7 +7473,7 @@
         </is>
       </c>
       <c r="B12" s="17">
-        <f>(E11/(1+Assumptions!$C$82)^0.5+F11/(1+Assumptions!$C$82)^1.5+G11/(1+Assumptions!$C$82)^2.5+H11/(1+Assumptions!$C$82)^3.5+I11/(1+Assumptions!$C$82)^4.5+I11*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(E11/(1+Assumptions!$C$82)^0.5+F11/(1+Assumptions!$C$82)^1.5+G11/(1+Assumptions!$C$82)^2.5+H11/(1+Assumptions!$C$82)^3.5+I11/(1+Assumptions!$C$82)^4.5+I11*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -7588,7 +7652,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -7774,7 +7838,7 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <f>(E30/(1+Assumptions!$C$82)^0.5+F30/(1+Assumptions!$C$82)^1.5+G30/(1+Assumptions!$C$82)^2.5+H30/(1+Assumptions!$C$82)^3.5+I30/(1+Assumptions!$C$82)^4.5+I30*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$23)/Equity_Roll!$C$21</f>
+        <f>(E30/(1+Assumptions!$C$82)^0.5+F30/(1+Assumptions!$C$82)^1.5+G30/(1+Assumptions!$C$82)^2.5+H30/(1+Assumptions!$C$82)^3.5+I30/(1+Assumptions!$C$82)^4.5+I30*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -8225,7 +8289,7 @@
         </is>
       </c>
       <c r="B9" s="53">
-        <f>DCF!D25&gt;0</f>
+        <f>DCF!D26&gt;0</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -8241,7 +8305,7 @@
         </is>
       </c>
       <c r="B10" s="53">
-        <f>ABS(Sensitivity!E8-DCF!D25)&lt;0.01</f>
+        <f>ABS(Sensitivity!E8-DCF!D26)&lt;0.01</f>
         <v/>
       </c>
       <c r="J10" s="11" t="inlineStr">
@@ -8464,11 +8528,11 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>FCFE!D18/DCF!D25</f>
+        <f>FCFE!D20/DCF!D26</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -8611,11 +8675,11 @@
         </is>
       </c>
       <c r="C5" s="14">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>DCF!D25</f>
+        <f>DCF!D26</f>
         <v/>
       </c>
       <c r="E5" s="15">
@@ -8776,11 +8840,11 @@
         </is>
       </c>
       <c r="C10" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>FCFE!D18</f>
+        <f>FCFE!D20</f>
         <v/>
       </c>
       <c r="E10" s="15">
@@ -9047,11 +9111,11 @@
         </is>
       </c>
       <c r="C7" s="24" t="n">
-        <v>9.6218</v>
+        <v>9.666700000000001</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17腾讯行情港元现价75.05 / fx7.8=9.6218美元</t>
+          <t>2026-08-17腾讯行情港元现价75.4 / fx7.8=9.6667美元</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9135,7 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>总市值6425.1亿港元/港元现价(腾讯行情 2026-08-17); 港股总市值=全部股本×港元价, 与A+H实际口径有差异</t>
+          <t>总市值6455.0亿港元/港元现价(腾讯行情 2026-08-17); 港股总市值=全部股本×港元价, 与A+H实际口径有差异</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9156,7 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>＝现价×总股本, 约824亿元, 与行情软件一致</t>
+          <t>＝现价×总股本, 约828亿元, 与行情软件一致</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12366,7 @@
         </is>
       </c>
       <c r="B4" s="25" t="n">
-        <v>0</v>
+        <v>6215.1</v>
       </c>
       <c r="C4" s="25" t="n">
         <v>6364.2</v>
@@ -12384,7 +12448,7 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>0</v>
+        <v>1170</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>840.2</v>
@@ -12548,7 +12612,7 @@
         </is>
       </c>
       <c r="B10" s="25" t="n">
-        <v>13529</v>
+        <v>6143.9</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>85.40000000000001</v>
@@ -12711,7 +12775,7 @@
         </is>
       </c>
       <c r="B14" s="25" t="n">
-        <v>0</v>
+        <v>33.7</v>
       </c>
       <c r="C14" s="25" t="n">
         <v>24.3</v>
@@ -12834,7 +12898,7 @@
         </is>
       </c>
       <c r="B17" s="25" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="C17" s="25" t="n">
         <v>29.2</v>
@@ -12916,7 +12980,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>-23945</v>
+        <v>10160.3</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>2484.9</v>
@@ -13205,7 +13269,7 @@
         </is>
       </c>
       <c r="B26" s="25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="C26" s="25" t="n">
         <v>84.8</v>
@@ -13328,7 +13392,7 @@
         </is>
       </c>
       <c r="B29" s="25" t="n">
-        <v>3873.7</v>
+        <v>3863.1</v>
       </c>
       <c r="C29" s="25" t="n">
         <v>901.8</v>
@@ -13409,7 +13473,7 @@
         </is>
       </c>
       <c r="B31" s="25" t="n">
-        <v>0</v>
+        <v>8334.6</v>
       </c>
       <c r="C31" s="25" t="n">
         <v>8038.1</v>
@@ -13491,7 +13555,7 @@
         </is>
       </c>
       <c r="B33" s="25" t="n">
-        <v>-26.3</v>
+        <v>-8360.9</v>
       </c>
       <c r="C33" s="25" t="n">
         <v>486</v>
@@ -13611,7 +13675,7 @@
         </is>
       </c>
       <c r="B36" s="25" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="C36" s="25" t="n">
         <v>31.9</v>
@@ -13652,7 +13716,7 @@
         </is>
       </c>
       <c r="B37" s="25" t="n">
-        <v>0</v>
+        <v>14117.1</v>
       </c>
       <c r="C37" s="25" t="n">
         <v>14266.4</v>
@@ -13857,7 +13921,7 @@
         </is>
       </c>
       <c r="B42" s="25" t="n">
-        <v>5746.7</v>
+        <v>15020.6</v>
       </c>
       <c r="C42" s="25" t="n">
         <v>-0.1</v>
@@ -13937,7 +14001,7 @@
         </is>
       </c>
       <c r="B44" s="25" t="n">
-        <v>0</v>
+        <v>10729.5</v>
       </c>
       <c r="C44" s="25" t="n">
         <v>11255.8</v>
@@ -14237,7 +14301,7 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>18891.6</v>
+        <v>2667.3</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>3223.1</v>
@@ -14372,7 +14436,7 @@
         </is>
       </c>
       <c r="B8" s="38" t="n">
-        <v>23785.8</v>
+        <v>3358.3</v>
       </c>
       <c r="C8" s="38" t="n">
         <v>3175.6</v>
@@ -14413,7 +14477,7 @@
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>-54065.4</v>
+        <v>-7633.4</v>
       </c>
       <c r="C9" s="25" t="n">
         <v>-7669.9</v>
@@ -14548,7 +14612,7 @@
         </is>
       </c>
       <c r="B12" s="38" t="n">
-        <v>-43966.4</v>
+        <v>-6207.6</v>
       </c>
       <c r="C12" s="38" t="n">
         <v>-4518.4</v>
@@ -14730,7 +14794,7 @@
         </is>
       </c>
       <c r="B16" s="38" t="n">
-        <v>17468.3</v>
+        <v>2466.3</v>
       </c>
       <c r="C16" s="38" t="n">
         <v>1608.3</v>
@@ -14861,7 +14925,7 @@
         </is>
       </c>
       <c r="B19" s="38" t="n">
-        <v>44019.4</v>
+        <v>6215.1</v>
       </c>
       <c r="C19" s="38" t="n">
         <v>6364.2</v>

--- a/examples/00981_中芯国际_估值模型.xlsx
+++ b/examples/00981_中芯国际_估值模型.xlsx
@@ -1,48 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="BS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CF" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="PPE" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="FIN" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="DCF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Checks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue_Segments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PPE" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FIN" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity_Roll" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FCFE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relative_Val" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="SCEN_SWITCH">Assumptions!$C$5</definedName>
-    <definedName name="WACC_USED">Assumptions!$C$82</definedName>
-    <definedName name="WACC_CALC">Assumptions!$C$80</definedName>
-    <definedName name="TERM_G">Assumptions!$C$83</definedName>
-    <definedName name="KE">Assumptions!$C$78</definedName>
-    <definedName name="KD">Assumptions!$C$79</definedName>
-    <definedName name="RF_RATE">Assumptions!$C$71</definedName>
-    <definedName name="ERP">Assumptions!$C$72</definedName>
-    <definedName name="BETA_U">Assumptions!$C$73</definedName>
+    <definedName name="WACC_USED">Assumptions!$C$83</definedName>
+    <definedName name="WACC_CALC">Assumptions!$C$81</definedName>
+    <definedName name="TERM_G">Assumptions!$C$84</definedName>
+    <definedName name="KE">Assumptions!$C$79</definedName>
+    <definedName name="KD">Assumptions!$C$80</definedName>
+    <definedName name="RF_RATE">Assumptions!$C$72</definedName>
+    <definedName name="ERP">Assumptions!$C$73</definedName>
+    <definedName name="BETA_U">Assumptions!$C$74</definedName>
     <definedName name="TAX_RATE_Y1">Assumptions!$C$33</definedName>
-    <definedName name="PAYOUT_Y1">Assumptions!$C$53</definedName>
-    <definedName name="MIN_CASH_PCT">Assumptions!$C$57</definedName>
+    <definedName name="PAYOUT_Y1">Assumptions!$C$54</definedName>
+    <definedName name="MIN_CASH_PCT">Assumptions!$C$58</definedName>
     <definedName name="SHARES_DIL">Equity_Roll!$C$21</definedName>
     <definedName name="DCF_PS">DCF!$D$26</definedName>
     <definedName name="FCFE_PS">FCFE!$D$20</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="1000" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -270,8 +270,8 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C21" s="4">
-        <f>TEXT(Assumptions!C80,"0.00%")&amp;" / "&amp;TEXT(Assumptions!C82,"0.00%")</f>
+        <f>TEXT(Assumptions!C81,"0.00%")&amp;" / "&amp;TEXT(Assumptions!C83,"0.00%")</f>
         <v/>
       </c>
     </row>
@@ -1374,23 +1374,23 @@
         </is>
       </c>
       <c r="E13" s="26">
-        <f>IS!E4*Assumptions!$C$57</f>
+        <f>IS!E4*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="F13" s="26">
-        <f>IS!F4*Assumptions!$C$57</f>
+        <f>IS!F4*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="G13" s="26">
-        <f>IS!G4*Assumptions!$C$57</f>
+        <f>IS!G4*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="H13" s="26">
-        <f>IS!H4*Assumptions!$C$57</f>
+        <f>IS!H4*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="I13" s="26">
-        <f>IS!I4*Assumptions!$C$57</f>
+        <f>IS!I4*Assumptions!$C$58</f>
         <v/>
       </c>
       <c r="J13" s="11" t="inlineStr">
@@ -1509,23 +1509,23 @@
         </is>
       </c>
       <c r="E19" s="26">
-        <f>Assumptions!C$58</f>
+        <f>Assumptions!C$59</f>
         <v/>
       </c>
       <c r="F19" s="26">
-        <f>Assumptions!D$58</f>
+        <f>Assumptions!D$59</f>
         <v/>
       </c>
       <c r="G19" s="26">
-        <f>Assumptions!E$58</f>
+        <f>Assumptions!E$59</f>
         <v/>
       </c>
       <c r="H19" s="26">
-        <f>Assumptions!F$58</f>
+        <f>Assumptions!F$59</f>
         <v/>
       </c>
       <c r="I19" s="26">
-        <f>Assumptions!G$58</f>
+        <f>Assumptions!G$59</f>
         <v/>
       </c>
       <c r="J19" s="11" t="inlineStr">
@@ -1737,23 +1737,23 @@
         </is>
       </c>
       <c r="E26" s="26">
-        <f>E25*Assumptions!$C$62</f>
+        <f>E25*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>F25*Assumptions!$C$62</f>
+        <f>F25*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>G25*Assumptions!$C$62</f>
+        <f>G25*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>H25*Assumptions!$C$62</f>
+        <f>H25*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>I25*Assumptions!$C$62</f>
+        <f>I25*Assumptions!$C$63</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -1808,23 +1808,23 @@
         </is>
       </c>
       <c r="E30" s="26">
-        <f>Assumptions!C$59</f>
+        <f>Assumptions!C$60</f>
         <v/>
       </c>
       <c r="F30" s="26">
-        <f>Assumptions!D$59</f>
+        <f>Assumptions!D$60</f>
         <v/>
       </c>
       <c r="G30" s="26">
-        <f>Assumptions!E$59</f>
+        <f>Assumptions!E$60</f>
         <v/>
       </c>
       <c r="H30" s="26">
-        <f>Assumptions!F$59</f>
+        <f>Assumptions!F$60</f>
         <v/>
       </c>
       <c r="I30" s="26">
-        <f>Assumptions!G$59</f>
+        <f>Assumptions!G$60</f>
         <v/>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -1940,23 +1940,23 @@
         </is>
       </c>
       <c r="E34" s="26">
-        <f>E33*Assumptions!$C$63</f>
+        <f>E33*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="F34" s="26">
-        <f>F33*Assumptions!$C$63</f>
+        <f>F33*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="G34" s="26">
-        <f>G33*Assumptions!$C$63</f>
+        <f>G33*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="H34" s="26">
-        <f>H33*Assumptions!$C$63</f>
+        <f>H33*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="I34" s="26">
-        <f>I33*Assumptions!$C$63</f>
+        <f>I33*Assumptions!$C$64</f>
         <v/>
       </c>
       <c r="J34" s="11" t="inlineStr">
@@ -2011,23 +2011,23 @@
         </is>
       </c>
       <c r="E38" s="26">
-        <f>Assumptions!C$60</f>
+        <f>Assumptions!C$61</f>
         <v/>
       </c>
       <c r="F38" s="26">
-        <f>Assumptions!D$60</f>
+        <f>Assumptions!D$61</f>
         <v/>
       </c>
       <c r="G38" s="26">
-        <f>Assumptions!E$60</f>
+        <f>Assumptions!E$61</f>
         <v/>
       </c>
       <c r="H38" s="26">
-        <f>Assumptions!F$60</f>
+        <f>Assumptions!F$61</f>
         <v/>
       </c>
       <c r="I38" s="26">
-        <f>Assumptions!G$60</f>
+        <f>Assumptions!G$61</f>
         <v/>
       </c>
       <c r="J38" s="11" t="inlineStr">
@@ -2207,23 +2207,23 @@
         </is>
       </c>
       <c r="E44" s="26">
-        <f>E43*Assumptions!$C$64</f>
+        <f>E43*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="F44" s="26">
-        <f>F43*Assumptions!$C$64</f>
+        <f>F43*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="G44" s="26">
-        <f>G43*Assumptions!$C$64</f>
+        <f>G43*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="H44" s="26">
-        <f>H43*Assumptions!$C$64</f>
+        <f>H43*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="I44" s="26">
-        <f>I43*Assumptions!$C$64</f>
+        <f>I43*Assumptions!$C$65</f>
         <v/>
       </c>
       <c r="J44" s="11" t="inlineStr">
@@ -2278,23 +2278,23 @@
         </is>
       </c>
       <c r="E48" s="26">
-        <f>Assumptions!C$61</f>
+        <f>Assumptions!C$62</f>
         <v/>
       </c>
       <c r="F48" s="26">
-        <f>Assumptions!D$61</f>
+        <f>Assumptions!D$62</f>
         <v/>
       </c>
       <c r="G48" s="26">
-        <f>Assumptions!E$61</f>
+        <f>Assumptions!E$62</f>
         <v/>
       </c>
       <c r="H48" s="26">
-        <f>Assumptions!F$61</f>
+        <f>Assumptions!F$62</f>
         <v/>
       </c>
       <c r="I48" s="26">
-        <f>Assumptions!G$61</f>
+        <f>Assumptions!G$62</f>
         <v/>
       </c>
       <c r="J48" s="11" t="inlineStr">
@@ -2410,23 +2410,23 @@
         </is>
       </c>
       <c r="E52" s="26">
-        <f>E51*Assumptions!$C$65</f>
+        <f>E51*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="F52" s="26">
-        <f>F51*Assumptions!$C$65</f>
+        <f>F51*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="G52" s="26">
-        <f>G51*Assumptions!$C$65</f>
+        <f>G51*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="H52" s="26">
-        <f>H51*Assumptions!$C$65</f>
+        <f>H51*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="I52" s="26">
-        <f>I51*Assumptions!$C$65</f>
+        <f>I51*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="J52" s="11" t="inlineStr">
@@ -2817,23 +2817,23 @@
         </is>
       </c>
       <c r="E66" s="26">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="F66" s="26">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="G66" s="26">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="H66" s="26">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="I66" s="26">
-        <f>Assumptions!$C$67</f>
+        <f>Assumptions!$C$68</f>
         <v/>
       </c>
       <c r="J66" s="11" t="inlineStr">
@@ -2902,23 +2902,23 @@
         </is>
       </c>
       <c r="E72" s="26">
-        <f>E18*Assumptions!$C$62+E29*Assumptions!$C$63+E37*Assumptions!$C$64+E47*Assumptions!$C$65</f>
+        <f>E18*Assumptions!$C$63+E29*Assumptions!$C$64+E37*Assumptions!$C$65+E47*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="F72" s="26">
-        <f>F18*Assumptions!$C$62+F29*Assumptions!$C$63+F37*Assumptions!$C$64+F47*Assumptions!$C$65</f>
+        <f>F18*Assumptions!$C$63+F29*Assumptions!$C$64+F37*Assumptions!$C$65+F47*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="G72" s="26">
-        <f>G18*Assumptions!$C$62+G29*Assumptions!$C$63+G37*Assumptions!$C$64+G47*Assumptions!$C$65</f>
+        <f>G18*Assumptions!$C$63+G29*Assumptions!$C$64+G37*Assumptions!$C$65+G47*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="H72" s="26">
-        <f>H18*Assumptions!$C$62+H29*Assumptions!$C$63+H37*Assumptions!$C$64+H47*Assumptions!$C$65</f>
+        <f>H18*Assumptions!$C$63+H29*Assumptions!$C$64+H37*Assumptions!$C$65+H47*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="I72" s="26">
-        <f>I18*Assumptions!$C$62+I29*Assumptions!$C$63+I37*Assumptions!$C$64+I47*Assumptions!$C$65</f>
+        <f>I18*Assumptions!$C$63+I29*Assumptions!$C$64+I37*Assumptions!$C$65+I47*Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -2929,23 +2929,23 @@
         </is>
       </c>
       <c r="E73" s="26">
-        <f>E6*Assumptions!$C$66</f>
+        <f>E6*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F73" s="26">
-        <f>F6*Assumptions!$C$66</f>
+        <f>F6*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="G73" s="26">
-        <f>G6*Assumptions!$C$66</f>
+        <f>G6*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="H73" s="26">
-        <f>H6*Assumptions!$C$66</f>
+        <f>H6*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="I73" s="26">
-        <f>I6*Assumptions!$C$66</f>
+        <f>I6*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -2983,23 +2983,23 @@
         </is>
       </c>
       <c r="E75" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E74)*(1-Assumptions!C$33)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E74)*(1-Assumptions!C$33)*(1-Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="F75" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F74)*(1-Assumptions!D$33)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F74)*(1-Assumptions!D$33)*(1-Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="G75" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G74)*(1-Assumptions!E$33)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G74)*(1-Assumptions!E$33)*(1-Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="H75" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H74)*(1-Assumptions!F$33)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H74)*(1-Assumptions!F$33)*(1-Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="I75" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I74)*(1-Assumptions!G$33)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I74)*(1-Assumptions!G$33)*(1-Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -3172,23 +3172,23 @@
         </is>
       </c>
       <c r="E82" s="26">
-        <f>(E18+E80)/2*Assumptions!$C$62+(E29+E32)/2*Assumptions!$C$63+(E37+E81)/2*Assumptions!$C$64+(E47+E50)/2*Assumptions!$C$65</f>
+        <f>(E18+E80)/2*Assumptions!$C$63+(E29+E32)/2*Assumptions!$C$64+(E37+E81)/2*Assumptions!$C$65+(E47+E50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="F82" s="26">
-        <f>(F18+F80)/2*Assumptions!$C$62+(F29+F32)/2*Assumptions!$C$63+(F37+F81)/2*Assumptions!$C$64+(F47+F50)/2*Assumptions!$C$65</f>
+        <f>(F18+F80)/2*Assumptions!$C$63+(F29+F32)/2*Assumptions!$C$64+(F37+F81)/2*Assumptions!$C$65+(F47+F50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="G82" s="26">
-        <f>(G18+G80)/2*Assumptions!$C$62+(G29+G32)/2*Assumptions!$C$63+(G37+G81)/2*Assumptions!$C$64+(G47+G50)/2*Assumptions!$C$65</f>
+        <f>(G18+G80)/2*Assumptions!$C$63+(G29+G32)/2*Assumptions!$C$64+(G37+G81)/2*Assumptions!$C$65+(G47+G50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="H82" s="26">
-        <f>(H18+H80)/2*Assumptions!$C$62+(H29+H32)/2*Assumptions!$C$63+(H37+H81)/2*Assumptions!$C$64+(H47+H50)/2*Assumptions!$C$65</f>
+        <f>(H18+H80)/2*Assumptions!$C$63+(H29+H32)/2*Assumptions!$C$64+(H37+H81)/2*Assumptions!$C$65+(H47+H50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="I82" s="26">
-        <f>(I18+I80)/2*Assumptions!$C$62+(I29+I32)/2*Assumptions!$C$63+(I37+I81)/2*Assumptions!$C$64+(I47+I50)/2*Assumptions!$C$65</f>
+        <f>(I18+I80)/2*Assumptions!$C$63+(I29+I32)/2*Assumptions!$C$64+(I37+I81)/2*Assumptions!$C$65+(I47+I50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -3226,23 +3226,23 @@
         </is>
       </c>
       <c r="E84" s="26">
-        <f>(E6+E83)/2*Assumptions!$C$66</f>
+        <f>(E6+E83)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F84" s="26">
-        <f>(F6+F83)/2*Assumptions!$C$66</f>
+        <f>(F6+F83)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="G84" s="26">
-        <f>(G6+G83)/2*Assumptions!$C$66</f>
+        <f>(G6+G83)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="H84" s="26">
-        <f>(H6+H83)/2*Assumptions!$C$66</f>
+        <f>(H6+H83)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="I84" s="26">
-        <f>(I6+I83)/2*Assumptions!$C$66</f>
+        <f>(I6+I83)/2*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -3395,23 +3395,23 @@
         </is>
       </c>
       <c r="E91" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E90)*(1-Assumptions!C$33)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E90)*(1-Assumptions!C$33)*(1-Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="F91" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F90)*(1-Assumptions!D$33)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F90)*(1-Assumptions!D$33)*(1-Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="G91" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G90)*(1-Assumptions!E$33)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G90)*(1-Assumptions!E$33)*(1-Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="H91" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H90)*(1-Assumptions!F$33)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H90)*(1-Assumptions!F$33)*(1-Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="I91" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I90)*(1-Assumptions!G$33)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I90)*(1-Assumptions!G$33)*(1-Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -3584,23 +3584,23 @@
         </is>
       </c>
       <c r="E98" s="26">
-        <f>(E18+E96)/2*Assumptions!$C$62+(E29+E32)/2*Assumptions!$C$63+(E37+E97)/2*Assumptions!$C$64+(E47+E50)/2*Assumptions!$C$65</f>
+        <f>(E18+E96)/2*Assumptions!$C$63+(E29+E32)/2*Assumptions!$C$64+(E37+E97)/2*Assumptions!$C$65+(E47+E50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="F98" s="26">
-        <f>(F18+F96)/2*Assumptions!$C$62+(F29+F32)/2*Assumptions!$C$63+(F37+F97)/2*Assumptions!$C$64+(F47+F50)/2*Assumptions!$C$65</f>
+        <f>(F18+F96)/2*Assumptions!$C$63+(F29+F32)/2*Assumptions!$C$64+(F37+F97)/2*Assumptions!$C$65+(F47+F50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="G98" s="26">
-        <f>(G18+G96)/2*Assumptions!$C$62+(G29+G32)/2*Assumptions!$C$63+(G37+G97)/2*Assumptions!$C$64+(G47+G50)/2*Assumptions!$C$65</f>
+        <f>(G18+G96)/2*Assumptions!$C$63+(G29+G32)/2*Assumptions!$C$64+(G37+G97)/2*Assumptions!$C$65+(G47+G50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="H98" s="26">
-        <f>(H18+H96)/2*Assumptions!$C$62+(H29+H32)/2*Assumptions!$C$63+(H37+H97)/2*Assumptions!$C$64+(H47+H50)/2*Assumptions!$C$65</f>
+        <f>(H18+H96)/2*Assumptions!$C$63+(H29+H32)/2*Assumptions!$C$64+(H37+H97)/2*Assumptions!$C$65+(H47+H50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="I98" s="26">
-        <f>(I18+I96)/2*Assumptions!$C$62+(I29+I32)/2*Assumptions!$C$63+(I37+I97)/2*Assumptions!$C$64+(I47+I50)/2*Assumptions!$C$65</f>
+        <f>(I18+I96)/2*Assumptions!$C$63+(I29+I32)/2*Assumptions!$C$64+(I37+I97)/2*Assumptions!$C$65+(I47+I50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -3638,23 +3638,23 @@
         </is>
       </c>
       <c r="E100" s="26">
-        <f>(E6+E99)/2*Assumptions!$C$66</f>
+        <f>(E6+E99)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F100" s="26">
-        <f>(F6+F99)/2*Assumptions!$C$66</f>
+        <f>(F6+F99)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="G100" s="26">
-        <f>(G6+G99)/2*Assumptions!$C$66</f>
+        <f>(G6+G99)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="H100" s="26">
-        <f>(H6+H99)/2*Assumptions!$C$66</f>
+        <f>(H6+H99)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="I100" s="26">
-        <f>(I6+I99)/2*Assumptions!$C$66</f>
+        <f>(I6+I99)/2*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -3807,23 +3807,23 @@
         </is>
       </c>
       <c r="E107" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E106)*(1-Assumptions!C$33)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E106)*(1-Assumptions!C$33)*(1-Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="F107" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F106)*(1-Assumptions!D$33)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F106)*(1-Assumptions!D$33)*(1-Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="G107" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G106)*(1-Assumptions!E$33)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G106)*(1-Assumptions!E$33)*(1-Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="H107" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H106)*(1-Assumptions!F$33)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H106)*(1-Assumptions!F$33)*(1-Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="I107" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I106)*(1-Assumptions!G$33)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I106)*(1-Assumptions!G$33)*(1-Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -3996,23 +3996,23 @@
         </is>
       </c>
       <c r="E114" s="26">
-        <f>(E18+E112)/2*Assumptions!$C$62+(E29+E32)/2*Assumptions!$C$63+(E37+E113)/2*Assumptions!$C$64+(E47+E50)/2*Assumptions!$C$65</f>
+        <f>(E18+E112)/2*Assumptions!$C$63+(E29+E32)/2*Assumptions!$C$64+(E37+E113)/2*Assumptions!$C$65+(E47+E50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="F114" s="26">
-        <f>(F18+F112)/2*Assumptions!$C$62+(F29+F32)/2*Assumptions!$C$63+(F37+F113)/2*Assumptions!$C$64+(F47+F50)/2*Assumptions!$C$65</f>
+        <f>(F18+F112)/2*Assumptions!$C$63+(F29+F32)/2*Assumptions!$C$64+(F37+F113)/2*Assumptions!$C$65+(F47+F50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="G114" s="26">
-        <f>(G18+G112)/2*Assumptions!$C$62+(G29+G32)/2*Assumptions!$C$63+(G37+G113)/2*Assumptions!$C$64+(G47+G50)/2*Assumptions!$C$65</f>
+        <f>(G18+G112)/2*Assumptions!$C$63+(G29+G32)/2*Assumptions!$C$64+(G37+G113)/2*Assumptions!$C$65+(G47+G50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="H114" s="26">
-        <f>(H18+H112)/2*Assumptions!$C$62+(H29+H32)/2*Assumptions!$C$63+(H37+H113)/2*Assumptions!$C$64+(H47+H50)/2*Assumptions!$C$65</f>
+        <f>(H18+H112)/2*Assumptions!$C$63+(H29+H32)/2*Assumptions!$C$64+(H37+H113)/2*Assumptions!$C$65+(H47+H50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="I114" s="26">
-        <f>(I18+I112)/2*Assumptions!$C$62+(I29+I32)/2*Assumptions!$C$63+(I37+I113)/2*Assumptions!$C$64+(I47+I50)/2*Assumptions!$C$65</f>
+        <f>(I18+I112)/2*Assumptions!$C$63+(I29+I32)/2*Assumptions!$C$64+(I37+I113)/2*Assumptions!$C$65+(I47+I50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -4050,23 +4050,23 @@
         </is>
       </c>
       <c r="E116" s="26">
-        <f>(E6+E115)/2*Assumptions!$C$66</f>
+        <f>(E6+E115)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F116" s="26">
-        <f>(F6+F115)/2*Assumptions!$C$66</f>
+        <f>(F6+F115)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="G116" s="26">
-        <f>(G6+G115)/2*Assumptions!$C$66</f>
+        <f>(G6+G115)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="H116" s="26">
-        <f>(H6+H115)/2*Assumptions!$C$66</f>
+        <f>(H6+H115)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="I116" s="26">
-        <f>(I6+I115)/2*Assumptions!$C$66</f>
+        <f>(I6+I115)/2*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -4219,23 +4219,23 @@
         </is>
       </c>
       <c r="E123" s="26">
-        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E122)*(1-Assumptions!C$33)</f>
+        <f>(IS!E7-IS!E9-IS!E10-IS!E11-IS!E12+IS!E14+IS!E16-E122)*(1-Assumptions!C$33)*(1-Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="F123" s="26">
-        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F122)*(1-Assumptions!D$33)</f>
+        <f>(IS!F7-IS!F9-IS!F10-IS!F11-IS!F12+IS!F14+IS!F16-F122)*(1-Assumptions!D$33)*(1-Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="G123" s="26">
-        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G122)*(1-Assumptions!E$33)</f>
+        <f>(IS!G7-IS!G9-IS!G10-IS!G11-IS!G12+IS!G14+IS!G16-G122)*(1-Assumptions!E$33)*(1-Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="H123" s="26">
-        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H122)*(1-Assumptions!F$33)</f>
+        <f>(IS!H7-IS!H9-IS!H10-IS!H11-IS!H12+IS!H14+IS!H16-H122)*(1-Assumptions!F$33)*(1-Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="I123" s="26">
-        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I122)*(1-Assumptions!G$33)</f>
+        <f>(IS!I7-IS!I9-IS!I10-IS!I11-IS!I12+IS!I14+IS!I16-I122)*(1-Assumptions!G$33)*(1-Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -4408,23 +4408,23 @@
         </is>
       </c>
       <c r="E130" s="26">
-        <f>(E18+E128)/2*Assumptions!$C$62+(E29+E32)/2*Assumptions!$C$63+(E37+E129)/2*Assumptions!$C$64+(E47+E50)/2*Assumptions!$C$65</f>
+        <f>(E18+E128)/2*Assumptions!$C$63+(E29+E32)/2*Assumptions!$C$64+(E37+E129)/2*Assumptions!$C$65+(E47+E50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="F130" s="26">
-        <f>(F18+F128)/2*Assumptions!$C$62+(F29+F32)/2*Assumptions!$C$63+(F37+F129)/2*Assumptions!$C$64+(F47+F50)/2*Assumptions!$C$65</f>
+        <f>(F18+F128)/2*Assumptions!$C$63+(F29+F32)/2*Assumptions!$C$64+(F37+F129)/2*Assumptions!$C$65+(F47+F50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="G130" s="26">
-        <f>(G18+G128)/2*Assumptions!$C$62+(G29+G32)/2*Assumptions!$C$63+(G37+G129)/2*Assumptions!$C$64+(G47+G50)/2*Assumptions!$C$65</f>
+        <f>(G18+G128)/2*Assumptions!$C$63+(G29+G32)/2*Assumptions!$C$64+(G37+G129)/2*Assumptions!$C$65+(G47+G50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="H130" s="26">
-        <f>(H18+H128)/2*Assumptions!$C$62+(H29+H32)/2*Assumptions!$C$63+(H37+H129)/2*Assumptions!$C$64+(H47+H50)/2*Assumptions!$C$65</f>
+        <f>(H18+H128)/2*Assumptions!$C$63+(H29+H32)/2*Assumptions!$C$64+(H37+H129)/2*Assumptions!$C$65+(H47+H50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
       <c r="I130" s="26">
-        <f>(I18+I128)/2*Assumptions!$C$62+(I29+I32)/2*Assumptions!$C$63+(I37+I129)/2*Assumptions!$C$64+(I47+I50)/2*Assumptions!$C$65</f>
+        <f>(I18+I128)/2*Assumptions!$C$63+(I29+I32)/2*Assumptions!$C$64+(I37+I129)/2*Assumptions!$C$65+(I47+I50)/2*Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
@@ -4462,23 +4462,23 @@
         </is>
       </c>
       <c r="E132" s="26">
-        <f>(E6+E131)/2*Assumptions!$C$66</f>
+        <f>(E6+E131)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="F132" s="26">
-        <f>(F6+F131)/2*Assumptions!$C$66</f>
+        <f>(F6+F131)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="G132" s="26">
-        <f>(G6+G131)/2*Assumptions!$C$66</f>
+        <f>(G6+G131)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="H132" s="26">
-        <f>(H6+H131)/2*Assumptions!$C$66</f>
+        <f>(H6+H131)/2*Assumptions!$C$67</f>
         <v/>
       </c>
       <c r="I132" s="26">
-        <f>(I6+I131)/2*Assumptions!$C$66</f>
+        <f>(I6+I131)/2*Assumptions!$C$67</f>
         <v/>
       </c>
     </row>
@@ -4582,23 +4582,23 @@
         </is>
       </c>
       <c r="E138" s="40">
-        <f>ABS(E65-(E6+E63)/2*Assumptions!$C$66)</f>
+        <f>ABS(E65-(E6+E63)/2*Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="F138" s="40">
-        <f>ABS(F65-(F6+F63)/2*Assumptions!$C$66)</f>
+        <f>ABS(F65-(F6+F63)/2*Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="G138" s="40">
-        <f>ABS(G65-(G6+G63)/2*Assumptions!$C$66)</f>
+        <f>ABS(G65-(G6+G63)/2*Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="H138" s="40">
-        <f>ABS(H65-(H6+H63)/2*Assumptions!$C$66)</f>
+        <f>ABS(H65-(H6+H63)/2*Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="I138" s="40">
-        <f>ABS(I65-(I6+I63)/2*Assumptions!$C$66)</f>
+        <f>ABS(I65-(I6+I63)/2*Assumptions!$C$67)</f>
         <v/>
       </c>
       <c r="J138" s="11" t="inlineStr">
@@ -4947,23 +4947,23 @@
         </is>
       </c>
       <c r="E9" s="26">
-        <f>IS!E20*Assumptions!$C$54</f>
+        <f>IS!E20*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>IS!F20*Assumptions!$C$54</f>
+        <f>IS!F20*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>IS!G20*Assumptions!$C$54</f>
+        <f>IS!G20*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>IS!H20*Assumptions!$C$54</f>
+        <f>IS!H20*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>IS!I20*Assumptions!$C$54</f>
+        <f>IS!I20*Assumptions!$C$55</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -5288,7 +5288,7 @@
           <t>稀释后股数(百万股)</t>
         </is>
       </c>
-      <c r="C21" s="37">
+      <c r="C21" s="38">
         <f>C19+C20</f>
         <v/>
       </c>
@@ -5387,23 +5387,23 @@
         </is>
       </c>
       <c r="E4" s="26">
-        <f>IS!E23</f>
+        <f>IS!E24</f>
         <v/>
       </c>
       <c r="F4" s="26">
-        <f>IS!F23</f>
+        <f>IS!F24</f>
         <v/>
       </c>
       <c r="G4" s="26">
-        <f>IS!G23</f>
+        <f>IS!G24</f>
         <v/>
       </c>
       <c r="H4" s="26">
-        <f>IS!H23</f>
+        <f>IS!H24</f>
         <v/>
       </c>
       <c r="I4" s="26">
-        <f>IS!I23</f>
+        <f>IS!I24</f>
         <v/>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -5618,23 +5618,23 @@
         </is>
       </c>
       <c r="E12" s="32">
-        <f>1/(1+Assumptions!$C$82)^E11</f>
+        <f>1/(1+Assumptions!$C$83)^E11</f>
         <v/>
       </c>
       <c r="F12" s="32">
-        <f>1/(1+Assumptions!$C$82)^F11</f>
+        <f>1/(1+Assumptions!$C$83)^F11</f>
         <v/>
       </c>
       <c r="G12" s="32">
-        <f>1/(1+Assumptions!$C$82)^G11</f>
+        <f>1/(1+Assumptions!$C$83)^G11</f>
         <v/>
       </c>
       <c r="H12" s="32">
-        <f>1/(1+Assumptions!$C$82)^H11</f>
+        <f>1/(1+Assumptions!$C$83)^H11</f>
         <v/>
       </c>
       <c r="I12" s="32">
-        <f>1/(1+Assumptions!$C$82)^I11</f>
+        <f>1/(1+Assumptions!$C$83)^I11</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr"/>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>I10*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)</f>
+        <f>I10*(1+Assumptions!$C$84)/(Assumptions!$C$83-Assumptions!$C$84)</f>
         <v/>
       </c>
       <c r="J16" s="11" t="inlineStr">
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="D30" s="44">
-        <f>D18/(IS!E23+PPE!E19)</f>
+        <f>D18/(IS!E24+PPE!E19)</f>
         <v/>
       </c>
       <c r="J30" s="11" t="inlineStr"/>
@@ -5935,7 +5935,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>单位: 美元百万元(财报口径) | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按g封顶)</t>
+          <t>单位: 美元百万元(财报口径) | FCFE=归母净利+D&amp;A-ΔNWC-Capex+净新增借款(FIN页调度); 按股权成本Ke折现(年中口径与DCF页一致), 直接得归母股权价值(少数股东权益见DCF页EV→Equity桥); 终值取正常化FCFE(净新增借款按D×g稳态正常化)</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
         </is>
       </c>
       <c r="D16" s="26">
-        <f>I10-I8+MIN(I8,FIN!I56*TERM_G)</f>
+        <f>I10-I8+FIN!I56*TERM_G</f>
         <v/>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>净新增借款按g封顶: 终值内净新增借款取MIN(实际调度, 2030E期末有息负债×g), 防止显性期末大额净融资被Gordon公式永续外推; 去杠杆/平稳年(实际≤封顶值)维持实际调度不变</t>
+          <t>终值净借款按D×g稳态正常化: 终值年净新增借款=2030E期末有息负债×g(替代实际调度值, 对称防止显性期末大额净融资/净偿还被Gordon公式永续外推)</t>
         </is>
       </c>
     </row>
@@ -6765,29 +6765,29 @@
         </is>
       </c>
       <c r="C5" s="43">
-        <f>Assumptions!$C$83-0.0100</f>
+        <f>Assumptions!$C$84-0.0100</f>
         <v/>
       </c>
       <c r="D5" s="43">
-        <f>Assumptions!$C$83-0.0050</f>
+        <f>Assumptions!$C$84-0.0050</f>
         <v/>
       </c>
       <c r="E5" s="43">
-        <f>Assumptions!$C$83</f>
+        <f>Assumptions!$C$84</f>
         <v/>
       </c>
       <c r="F5" s="43">
-        <f>Assumptions!$C$83+0.0050</f>
+        <f>Assumptions!$C$84+0.0050</f>
         <v/>
       </c>
       <c r="G5" s="43">
-        <f>Assumptions!$C$83+0.0100</f>
+        <f>Assumptions!$C$84+0.0100</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="43">
-        <f>Assumptions!$C$82-0.0100</f>
+        <f>Assumptions!$C$83-0.0100</f>
         <v/>
       </c>
       <c r="C6" s="14">
@@ -6813,7 +6813,7 @@
     </row>
     <row r="7">
       <c r="B7" s="43">
-        <f>Assumptions!$C$82-0.0050</f>
+        <f>Assumptions!$C$83-0.0050</f>
         <v/>
       </c>
       <c r="C7" s="14">
@@ -6839,7 +6839,7 @@
     </row>
     <row r="8">
       <c r="B8" s="43">
-        <f>Assumptions!$C$82</f>
+        <f>Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="C8" s="14">
@@ -6865,7 +6865,7 @@
     </row>
     <row r="9">
       <c r="B9" s="43">
-        <f>Assumptions!$C$82+0.0050</f>
+        <f>Assumptions!$C$83+0.0050</f>
         <v/>
       </c>
       <c r="C9" s="14">
@@ -6891,7 +6891,7 @@
     </row>
     <row r="10">
       <c r="B10" s="43">
-        <f>Assumptions!$C$82+0.0100</f>
+        <f>Assumptions!$C$83+0.0100</f>
         <v/>
       </c>
       <c r="C10" s="14">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>机制: DPO变动δ→应付变动→ΔNWC变动→FCFF一阶调整; 未反映利息二阶效应(金额小); δ=0格=DCF基准</t>
+          <t>机制: DPO变动δ→应付变动→ΔNWC变动→FCFF一阶调整; 首年按全额COGS重定价, 以后年按ΔCOGS; 未反映利息二阶效应(金额小); δ=0格=DCF基准</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
         <v>-40</v>
       </c>
       <c r="C25" s="14">
-        <f>((DCF!E$10+$B25/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B25/365*(IS!E$6))/(1+Assumptions!$C$83)^0.5+(DCF!F$10+$B25/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$83)^1.5+(DCF!G$10+$B25/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$83)^2.5+(DCF!H$10+$B25/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$83)^3.5+(DCF!I$10+$B25/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$83)^4.5+(DCF!$I$10+$B25/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$84)/(Assumptions!$C$83-Assumptions!$C$84)/(1+Assumptions!$C$83)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D25" s="16">
@@ -7182,7 +7182,7 @@
         <v>-20</v>
       </c>
       <c r="C26" s="14">
-        <f>((DCF!E$10+$B26/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B26/365*(IS!E$6))/(1+Assumptions!$C$83)^0.5+(DCF!F$10+$B26/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$83)^1.5+(DCF!G$10+$B26/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$83)^2.5+(DCF!H$10+$B26/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$83)^3.5+(DCF!I$10+$B26/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$83)^4.5+(DCF!$I$10+$B26/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$84)/(Assumptions!$C$83-Assumptions!$C$84)/(1+Assumptions!$C$83)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D26" s="16">
@@ -7195,7 +7195,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="48">
-        <f>((DCF!E$10+$B27/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B27/365*(IS!E$6))/(1+Assumptions!$C$83)^0.5+(DCF!F$10+$B27/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$83)^1.5+(DCF!G$10+$B27/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$83)^2.5+(DCF!H$10+$B27/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$83)^3.5+(DCF!I$10+$B27/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$83)^4.5+(DCF!$I$10+$B27/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$84)/(Assumptions!$C$83-Assumptions!$C$84)/(1+Assumptions!$C$83)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D27" s="16">
@@ -7208,7 +7208,7 @@
         <v>20</v>
       </c>
       <c r="C28" s="14">
-        <f>((DCF!E$10+$B28/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B28/365*(IS!E$6))/(1+Assumptions!$C$83)^0.5+(DCF!F$10+$B28/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$83)^1.5+(DCF!G$10+$B28/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$83)^2.5+(DCF!H$10+$B28/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$83)^3.5+(DCF!I$10+$B28/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$83)^4.5+(DCF!$I$10+$B28/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$84)/(Assumptions!$C$83-Assumptions!$C$84)/(1+Assumptions!$C$83)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D28" s="16">
@@ -7221,7 +7221,7 @@
         <v>40</v>
       </c>
       <c r="C29" s="14">
-        <f>((DCF!E$10+$B29/365*(IS!E$6-IS!D$6))/(1+Assumptions!$C$82)^0.5+(DCF!F$10+$B29/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$82)^1.5+(DCF!G$10+$B29/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$82)^2.5+(DCF!H$10+$B29/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$82)^3.5+(DCF!I$10+$B29/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$82)^4.5+(DCF!$I$10+$B29/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>((DCF!E$10+$B29/365*(IS!E$6))/(1+Assumptions!$C$83)^0.5+(DCF!F$10+$B29/365*(IS!F$6-IS!E$6))/(1+Assumptions!$C$83)^1.5+(DCF!G$10+$B29/365*(IS!G$6-IS!F$6))/(1+Assumptions!$C$83)^2.5+(DCF!H$10+$B29/365*(IS!H$6-IS!G$6))/(1+Assumptions!$C$83)^3.5+(DCF!I$10+$B29/365*(IS!I$6-IS!H$6))/(1+Assumptions!$C$83)^4.5+(DCF!$I$10+$B29/365*(IS!I$6-IS!H$6))*(1+Assumptions!$C$84)/(Assumptions!$C$83-Assumptions!$C$84)/(1+Assumptions!$C$83)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="D29" s="16">
@@ -7232,7 +7232,7 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>DPO每±20天≈FCFF±(Δ营业成本×20/365); 基准DPO路径见Assumptions(147→147天)</t>
+          <t>DPO每±20天: 首年≈FCFF±(营业成本×20/365), 以后年≈±(Δ营业成本×20/365); 基准DPO路径见Assumptions(147→147天)</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>熊市 Bear — 收入增速调整/净利率调整引用Assumptions第87行</t>
+          <t>熊市 Bear — 收入增速调整/净利率调整引用Assumptions第88行</t>
         </is>
       </c>
     </row>
@@ -7365,23 +7365,23 @@
         </is>
       </c>
       <c r="E8" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E21+Assumptions!$C$87)</f>
+        <f>IS!D4*(1+Revenue_Segments!E21+Assumptions!$C$88)</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>E8*(1+Revenue_Segments!F21+Assumptions!$C$87)</f>
+        <f>E8*(1+Revenue_Segments!F21+Assumptions!$C$88)</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>F8*(1+Revenue_Segments!G21+Assumptions!$C$87)</f>
+        <f>F8*(1+Revenue_Segments!G21+Assumptions!$C$88)</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>G8*(1+Revenue_Segments!H21+Assumptions!$C$87)</f>
+        <f>G8*(1+Revenue_Segments!H21+Assumptions!$C$88)</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>H8*(1+Revenue_Segments!I21+Assumptions!$C$87)</f>
+        <f>H8*(1+Revenue_Segments!I21+Assumptions!$C$88)</f>
         <v/>
       </c>
     </row>
@@ -7392,23 +7392,23 @@
         </is>
       </c>
       <c r="E9" s="16">
-        <f>(Revenue_Segments!E22+Assumptions!$D$87-Assumptions!C$27-Assumptions!C$28-Assumptions!C$29-Assumptions!C$30-Assumptions!$C$34)*(1-Assumptions!C$33)</f>
+        <f>(Revenue_Segments!E22+Assumptions!$D$88-Assumptions!C$27-Assumptions!C$28-Assumptions!C$29-Assumptions!C$30-Assumptions!$C$35)*(1-Assumptions!C$33)*(1-Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(Revenue_Segments!F22+Assumptions!$D$87-Assumptions!D$27-Assumptions!D$28-Assumptions!D$29-Assumptions!D$30-Assumptions!$C$34)*(1-Assumptions!D$33)</f>
+        <f>(Revenue_Segments!F22+Assumptions!$D$88-Assumptions!D$27-Assumptions!D$28-Assumptions!D$29-Assumptions!D$30-Assumptions!$C$35)*(1-Assumptions!D$33)*(1-Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>(Revenue_Segments!G22+Assumptions!$D$87-Assumptions!E$27-Assumptions!E$28-Assumptions!E$29-Assumptions!E$30-Assumptions!$C$34)*(1-Assumptions!E$33)</f>
+        <f>(Revenue_Segments!G22+Assumptions!$D$88-Assumptions!E$27-Assumptions!E$28-Assumptions!E$29-Assumptions!E$30-Assumptions!$C$35)*(1-Assumptions!E$33)*(1-Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>(Revenue_Segments!H22+Assumptions!$D$87-Assumptions!F$27-Assumptions!F$28-Assumptions!F$29-Assumptions!F$30-Assumptions!$C$34)*(1-Assumptions!F$33)</f>
+        <f>(Revenue_Segments!H22+Assumptions!$D$88-Assumptions!F$27-Assumptions!F$28-Assumptions!F$29-Assumptions!F$30-Assumptions!$C$35)*(1-Assumptions!F$33)*(1-Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>(Revenue_Segments!I22+Assumptions!$D$87-Assumptions!G$27-Assumptions!G$28-Assumptions!G$29-Assumptions!G$30-Assumptions!$C$34)*(1-Assumptions!G$33)</f>
+        <f>(Revenue_Segments!I22+Assumptions!$D$88-Assumptions!G$27-Assumptions!G$28-Assumptions!G$29-Assumptions!G$30-Assumptions!$C$35)*(1-Assumptions!G$33)*(1-Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         </is>
       </c>
       <c r="B12" s="17">
-        <f>(E11/(1+Assumptions!$C$82)^0.5+F11/(1+Assumptions!$C$82)^1.5+G11/(1+Assumptions!$C$82)^2.5+H11/(1+Assumptions!$C$82)^3.5+I11/(1+Assumptions!$C$82)^4.5+I11*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>(E11/(1+Assumptions!$C$83)^0.5+F11/(1+Assumptions!$C$83)^1.5+G11/(1+Assumptions!$C$83)^2.5+H11/(1+Assumptions!$C$83)^3.5+I11/(1+Assumptions!$C$83)^4.5+I11*(1+Assumptions!$C$84)/(Assumptions!$C$83-Assumptions!$C$84)/(1+Assumptions!$C$83)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J12" s="11" t="inlineStr">
@@ -7501,7 +7501,7 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>基准 Base — 收入增速调整/净利率调整引用Assumptions第88行</t>
+          <t>基准 Base — 收入增速调整/净利率调整引用Assumptions第89行</t>
         </is>
       </c>
     </row>
@@ -7544,23 +7544,23 @@
         </is>
       </c>
       <c r="E17" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E21+Assumptions!$C$88)</f>
+        <f>IS!D4*(1+Revenue_Segments!E21+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="F17" s="26">
-        <f>E17*(1+Revenue_Segments!F21+Assumptions!$C$88)</f>
+        <f>E17*(1+Revenue_Segments!F21+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="G17" s="26">
-        <f>F17*(1+Revenue_Segments!G21+Assumptions!$C$88)</f>
+        <f>F17*(1+Revenue_Segments!G21+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="H17" s="26">
-        <f>G17*(1+Revenue_Segments!H21+Assumptions!$C$88)</f>
+        <f>G17*(1+Revenue_Segments!H21+Assumptions!$C$89)</f>
         <v/>
       </c>
       <c r="I17" s="26">
-        <f>H17*(1+Revenue_Segments!I21+Assumptions!$C$88)</f>
+        <f>H17*(1+Revenue_Segments!I21+Assumptions!$C$89)</f>
         <v/>
       </c>
     </row>
@@ -7571,23 +7571,23 @@
         </is>
       </c>
       <c r="E18" s="16">
-        <f>(Revenue_Segments!E22+Assumptions!$D$88-Assumptions!C$27-Assumptions!C$28-Assumptions!C$29-Assumptions!C$30-Assumptions!$C$34)*(1-Assumptions!C$33)</f>
+        <f>(Revenue_Segments!E22+Assumptions!$D$89-Assumptions!C$27-Assumptions!C$28-Assumptions!C$29-Assumptions!C$30-Assumptions!$C$35)*(1-Assumptions!C$33)*(1-Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>(Revenue_Segments!F22+Assumptions!$D$88-Assumptions!D$27-Assumptions!D$28-Assumptions!D$29-Assumptions!D$30-Assumptions!$C$34)*(1-Assumptions!D$33)</f>
+        <f>(Revenue_Segments!F22+Assumptions!$D$89-Assumptions!D$27-Assumptions!D$28-Assumptions!D$29-Assumptions!D$30-Assumptions!$C$35)*(1-Assumptions!D$33)*(1-Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>(Revenue_Segments!G22+Assumptions!$D$88-Assumptions!E$27-Assumptions!E$28-Assumptions!E$29-Assumptions!E$30-Assumptions!$C$34)*(1-Assumptions!E$33)</f>
+        <f>(Revenue_Segments!G22+Assumptions!$D$89-Assumptions!E$27-Assumptions!E$28-Assumptions!E$29-Assumptions!E$30-Assumptions!$C$35)*(1-Assumptions!E$33)*(1-Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>(Revenue_Segments!H22+Assumptions!$D$88-Assumptions!F$27-Assumptions!F$28-Assumptions!F$29-Assumptions!F$30-Assumptions!$C$34)*(1-Assumptions!F$33)</f>
+        <f>(Revenue_Segments!H22+Assumptions!$D$89-Assumptions!F$27-Assumptions!F$28-Assumptions!F$29-Assumptions!F$30-Assumptions!$C$35)*(1-Assumptions!F$33)*(1-Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>(Revenue_Segments!I22+Assumptions!$D$88-Assumptions!G$27-Assumptions!G$28-Assumptions!G$29-Assumptions!G$30-Assumptions!$C$34)*(1-Assumptions!G$33)</f>
+        <f>(Revenue_Segments!I22+Assumptions!$D$89-Assumptions!G$27-Assumptions!G$28-Assumptions!G$29-Assumptions!G$30-Assumptions!$C$35)*(1-Assumptions!G$33)*(1-Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -7687,7 +7687,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>牛市 Bull — 收入增速调整/净利率调整引用Assumptions第89行</t>
+          <t>牛市 Bull — 收入增速调整/净利率调整引用Assumptions第90行</t>
         </is>
       </c>
     </row>
@@ -7730,23 +7730,23 @@
         </is>
       </c>
       <c r="E27" s="26">
-        <f>IS!D4*(1+Revenue_Segments!E21+Assumptions!$C$89)</f>
+        <f>IS!D4*(1+Revenue_Segments!E21+Assumptions!$C$90)</f>
         <v/>
       </c>
       <c r="F27" s="26">
-        <f>E27*(1+Revenue_Segments!F21+Assumptions!$C$89)</f>
+        <f>E27*(1+Revenue_Segments!F21+Assumptions!$C$90)</f>
         <v/>
       </c>
       <c r="G27" s="26">
-        <f>F27*(1+Revenue_Segments!G21+Assumptions!$C$89)</f>
+        <f>F27*(1+Revenue_Segments!G21+Assumptions!$C$90)</f>
         <v/>
       </c>
       <c r="H27" s="26">
-        <f>G27*(1+Revenue_Segments!H21+Assumptions!$C$89)</f>
+        <f>G27*(1+Revenue_Segments!H21+Assumptions!$C$90)</f>
         <v/>
       </c>
       <c r="I27" s="26">
-        <f>H27*(1+Revenue_Segments!I21+Assumptions!$C$89)</f>
+        <f>H27*(1+Revenue_Segments!I21+Assumptions!$C$90)</f>
         <v/>
       </c>
     </row>
@@ -7757,23 +7757,23 @@
         </is>
       </c>
       <c r="E28" s="16">
-        <f>(Revenue_Segments!E22+Assumptions!$D$89-Assumptions!C$27-Assumptions!C$28-Assumptions!C$29-Assumptions!C$30-Assumptions!$C$34)*(1-Assumptions!C$33)</f>
+        <f>(Revenue_Segments!E22+Assumptions!$D$90-Assumptions!C$27-Assumptions!C$28-Assumptions!C$29-Assumptions!C$30-Assumptions!$C$35)*(1-Assumptions!C$33)*(1-Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>(Revenue_Segments!F22+Assumptions!$D$89-Assumptions!D$27-Assumptions!D$28-Assumptions!D$29-Assumptions!D$30-Assumptions!$C$34)*(1-Assumptions!D$33)</f>
+        <f>(Revenue_Segments!F22+Assumptions!$D$90-Assumptions!D$27-Assumptions!D$28-Assumptions!D$29-Assumptions!D$30-Assumptions!$C$35)*(1-Assumptions!D$33)*(1-Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>(Revenue_Segments!G22+Assumptions!$D$89-Assumptions!E$27-Assumptions!E$28-Assumptions!E$29-Assumptions!E$30-Assumptions!$C$34)*(1-Assumptions!E$33)</f>
+        <f>(Revenue_Segments!G22+Assumptions!$D$90-Assumptions!E$27-Assumptions!E$28-Assumptions!E$29-Assumptions!E$30-Assumptions!$C$35)*(1-Assumptions!E$33)*(1-Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>(Revenue_Segments!H22+Assumptions!$D$89-Assumptions!F$27-Assumptions!F$28-Assumptions!F$29-Assumptions!F$30-Assumptions!$C$34)*(1-Assumptions!F$33)</f>
+        <f>(Revenue_Segments!H22+Assumptions!$D$90-Assumptions!F$27-Assumptions!F$28-Assumptions!F$29-Assumptions!F$30-Assumptions!$C$35)*(1-Assumptions!F$33)*(1-Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>(Revenue_Segments!I22+Assumptions!$D$89-Assumptions!G$27-Assumptions!G$28-Assumptions!G$29-Assumptions!G$30-Assumptions!$C$34)*(1-Assumptions!G$33)</f>
+        <f>(Revenue_Segments!I22+Assumptions!$D$90-Assumptions!G$27-Assumptions!G$28-Assumptions!G$29-Assumptions!G$30-Assumptions!$C$35)*(1-Assumptions!G$33)*(1-Assumptions!G$34)</f>
         <v/>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
         </is>
       </c>
       <c r="B31" s="17">
-        <f>(E30/(1+Assumptions!$C$82)^0.5+F30/(1+Assumptions!$C$82)^1.5+G30/(1+Assumptions!$C$82)^2.5+H30/(1+Assumptions!$C$82)^3.5+I30/(1+Assumptions!$C$82)^4.5+I30*(1+Assumptions!$C$83)/(Assumptions!$C$82-Assumptions!$C$83)/(1+Assumptions!$C$82)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
+        <f>(E30/(1+Assumptions!$C$83)^0.5+F30/(1+Assumptions!$C$83)^1.5+G30/(1+Assumptions!$C$83)^2.5+H30/(1+Assumptions!$C$83)^3.5+I30/(1+Assumptions!$C$83)^4.5+I30*(1+Assumptions!$C$84)/(Assumptions!$C$83-Assumptions!$C$84)/(1+Assumptions!$C$83)^4.5+DCF!$D$24)/Equity_Roll!$C$21</f>
         <v/>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -8241,7 +8241,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>5. 毛利率处于(0,60%)合理区间</t>
+          <t>5. 信息项(不闸门): 毛利率处于(0%,60%)区间</t>
         </is>
       </c>
       <c r="B8" s="53">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>防止假设越界</t>
+          <t>信息行, 不参与布尔汇总; 越界仅提示复核毛利率假设; 区间可经checks.gm_band配置</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="B11" s="53">
-        <f>OR(ABS(Assumptions!C82-Assumptions!C80)&lt;0.000001,Assumptions!C81&lt;&gt;"")</f>
+        <f>OR(ABS(Assumptions!C83-Assumptions!C81)&lt;0.000001,Assumptions!C82&lt;&gt;"")</f>
         <v/>
       </c>
       <c r="J11" s="11" t="inlineStr">
@@ -8508,11 +8508,11 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>Assumptions!C80</f>
+        <f>Assumptions!C81</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>Assumptions!C82</f>
+        <f>Assumptions!C83</f>
         <v/>
       </c>
       <c r="J20" s="11" t="inlineStr">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="F24" s="56">
-        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15),"全部通过=TRUE","存在未通过=FALSE")</f>
+        <f>IF(AND(B4:I4,E5:I5,E6:I6,B7:I7,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15),"全部通过=TRUE","存在未通过=FALSE")</f>
         <v/>
       </c>
     </row>
@@ -8579,7 +8579,7 @@
         </is>
       </c>
       <c r="F25" s="27">
-        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B8:I8,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15)</f>
+        <f>AND(B4:I4,E5:I5,E6:I6,B7:I7,B9,B10,B11,E12:I12,E13:I13,E14:I14,B15)</f>
         <v/>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17腾讯行情港元现价75.4 / fx7.8=9.6667美元</t>
+          <t>港元现价(=price 9.6667×fx 7.8回推, 保证price_hkd/fx_hkd与price完全一致; 2026-08-17腾讯行情原始值75.4); build_model按price_hkd/fx_hkd重折算模型价 | =港元75.4003/fx7.8=9.6667</t>
         </is>
       </c>
     </row>
@@ -9636,66 +9636,66 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>少数股东损益占净利润比</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>0.276654</v>
+      </c>
+      <c r="D34" s="28" t="n">
+        <v>0.276654</v>
+      </c>
+      <c r="E34" s="28" t="n">
+        <v>0.276654</v>
+      </c>
+      <c r="F34" s="28" t="n">
+        <v>0.276654</v>
+      </c>
+      <c r="G34" s="28" t="n">
+        <v>0.276654</v>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>按历史均值自动推导: (合并净利-归母)/合并净利 3年均值+27.67%, clamp[0,50%]→采用27.67%; config可经model.mi_share覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>其他及财务费用率合计(情景页用)</t>
         </is>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C34" s="28" t="n">
+      <c r="C35" s="28" t="n">
         <v>-0.0027</v>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>自动推导: 最近年报财务费用率, 供Scenarios页简化净利率计算</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>六、营运资本天数</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>DSO 应收(票据+账款)天数</t>
-        </is>
-      </c>
-      <c r="B37" s="21" t="inlineStr">
-        <is>
-          <t>天</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="D37" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="E37" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="F37" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="G37" s="30" t="n">
-        <v>56</v>
-      </c>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>自动推导: 最近年报DSO 56天持平</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>DIO 存货天数</t>
+          <t>DSO 应收(票据+账款)天数</t>
         </is>
       </c>
       <c r="B38" s="21" t="inlineStr">
@@ -9704,30 +9704,30 @@
         </is>
       </c>
       <c r="C38" s="30" t="n">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="D38" s="30" t="n">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="E38" s="30" t="n">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>180</v>
+        <v>56</v>
       </c>
       <c r="H38" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报DIO 180天持平</t>
+          <t>自动推导: 最近年报DSO 56天持平</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>DPO 应付(票据+账款)天数</t>
+          <t>DIO 存货天数</t>
         </is>
       </c>
       <c r="B39" s="21" t="inlineStr">
@@ -9736,62 +9736,62 @@
         </is>
       </c>
       <c r="C39" s="30" t="n">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="D39" s="30" t="n">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="E39" s="30" t="n">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报DPO 147天持平</t>
+          <t>自动推导: 最近年报DIO 180天持平</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>预付款项/收入</t>
+          <t>DPO 应付(票据+账款)天数</t>
         </is>
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C40" s="28" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="D40" s="28" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="E40" s="28" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="F40" s="28" t="n">
-        <v>0.0072</v>
-      </c>
-      <c r="G40" s="28" t="n">
-        <v>0.0072</v>
+          <t>天</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>147</v>
+      </c>
+      <c r="D40" s="30" t="n">
+        <v>147</v>
+      </c>
+      <c r="E40" s="30" t="n">
+        <v>147</v>
+      </c>
+      <c r="F40" s="30" t="n">
+        <v>147</v>
+      </c>
+      <c r="G40" s="30" t="n">
+        <v>147</v>
       </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报预付/收入持平</t>
+          <t>自动推导: 最近年报DPO 147天持平</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>应付职工薪酬/收入</t>
+          <t>预付款项/收入</t>
         </is>
       </c>
       <c r="B41" s="21" t="inlineStr">
@@ -9800,101 +9800,101 @@
         </is>
       </c>
       <c r="C41" s="28" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="D41" s="28" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="E41" s="28" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="F41" s="28" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="G41" s="28" t="n">
-        <v>0</v>
+        <v>0.0072</v>
       </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>自动推导: 最近年报应付职工薪酬/收入持平</t>
+          <t>自动推导: 最近年报预付/收入持平</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>应付职工薪酬/收入</t>
+        </is>
+      </c>
+      <c r="B42" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>自动推导: 最近年报应付职工薪酬/收入持平</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t>应交税费/收入</t>
         </is>
       </c>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C42" s="28" t="n">
+      <c r="C43" s="28" t="n">
         <v>0.0036</v>
       </c>
-      <c r="D42" s="28" t="n">
+      <c r="D43" s="28" t="n">
         <v>0.0036</v>
       </c>
-      <c r="E42" s="28" t="n">
+      <c r="E43" s="28" t="n">
         <v>0.0036</v>
       </c>
-      <c r="F42" s="28" t="n">
+      <c r="F43" s="28" t="n">
         <v>0.0036</v>
       </c>
-      <c r="G42" s="28" t="n">
+      <c r="G43" s="28" t="n">
         <v>0.0036</v>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>自动推导: 最近年报应交税费/收入持平</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>七、资本开支与折旧摊销 (PP&amp;E页驱动)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Capex占收入比</t>
-        </is>
-      </c>
-      <c r="B45" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C45" s="28" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D45" s="28" t="n">
-        <v>0.2975</v>
-      </c>
-      <c r="E45" s="28" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="F45" s="28" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G45" s="28" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>自动推导: 最近年报Capex/收入90.1%(上限35%)逐年退坡×1/.85/.70/.60/.50</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>在建工程转固率</t>
+          <t>Capex占收入比</t>
         </is>
       </c>
       <c r="B46" s="21" t="inlineStr">
@@ -9903,18 +9903,30 @@
         </is>
       </c>
       <c r="C46" s="28" t="n">
-        <v>0.75</v>
+        <v>0.35</v>
+      </c>
+      <c r="D46" s="28" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="E46" s="28" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="F46" s="28" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G46" s="28" t="n">
+        <v>0.175</v>
       </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 当年转固=(期初在建+当年Capex)×75%</t>
+          <t>自动推导: 最近年报Capex/收入90.1%(上限35%)逐年退坡×1/.85/.70/.60/.50</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>固定资产折旧率(期初净值)</t>
+          <t>在建工程转固率</t>
         </is>
       </c>
       <c r="B47" s="21" t="inlineStr">
@@ -9923,18 +9935,18 @@
         </is>
       </c>
       <c r="C47" s="28" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 固定资产净值口径12%</t>
+          <t>通用默认: 当年转固=(期初在建+当年Capex)×75%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>当年转固部分折旧率</t>
+          <t>固定资产折旧率(期初净值)</t>
         </is>
       </c>
       <c r="B48" s="21" t="inlineStr">
@@ -9943,18 +9955,18 @@
         </is>
       </c>
       <c r="C48" s="28" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 转固按约半年投产计提</t>
+          <t>通用默认: 固定资产净值口径12%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>固定资产处置率(期初净值)</t>
+          <t>当年转固部分折旧率</t>
         </is>
       </c>
       <c r="B49" s="21" t="inlineStr">
@@ -9963,156 +9975,144 @@
         </is>
       </c>
       <c r="C49" s="28" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 处置率1%</t>
+          <t>通用默认: 转固按约半年投产计提</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
+          <t>固定资产处置率(期初净值)</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C50" s="28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: 处置率1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>无形资产摊销率(期初)</t>
         </is>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C50" s="28" t="n">
+      <c r="C51" s="28" t="n">
         <v>0.08</v>
       </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H51" s="9" t="inlineStr">
         <is>
           <t>通用默认: 无形资产摊销率8%</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>八、股利与盈余公积</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>股利支付率(按上年归母)</t>
-        </is>
-      </c>
-      <c r="B53" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C53" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D53" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E53" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F53" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G53" s="28" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>通用默认: 股利支付率30%(按上年归母)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
+          <t>股利支付率(按上年归母)</t>
+        </is>
+      </c>
+      <c r="B54" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D54" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E54" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F54" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G54" s="28" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: 股利支付率30%(按上年归母)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
           <t>法定盈余公积计提率(按当年归母)</t>
         </is>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C54" s="28" t="n">
+      <c r="C55" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t>IFRS无法定盈余公积科目, 计提率置0</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="19" t="inlineStr">
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>九、债务与融资 (FIN页调度输入)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>最低现金占收入比</t>
-        </is>
-      </c>
-      <c r="B57" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C57" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H57" s="9" t="inlineStr">
-        <is>
-          <t>分析师修正: 2025年报货币资金5,872百万美元≈收入63%; 公司处扩产周期, 高额现金为资本开支储备, 不参与sweep偿债; 若按通用默认2%则期初存量现金被一次性sweep还债, FCFE首年机制性深负</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>短期借款(revolver)计划还款</t>
+          <t>最低现金占收入比</t>
         </is>
       </c>
       <c r="B58" s="21" t="inlineStr">
         <is>
-          <t>百万</t>
-        </is>
-      </c>
-      <c r="C58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="29" t="n">
-        <v>0</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C58" s="28" t="n">
+        <v>0.6</v>
       </c>
       <c r="H58" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 短借为revolver, 无计划还款</t>
+          <t>分析师修正: 2025年报货币资金5,872百万美元≈收入63%; 公司处扩产周期, 高额现金为资本开支储备, 不参与sweep偿债; 若按通用默认2%则期初存量现金被一次性sweep还债, FCFE首年机制性深负</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>一年内到期非流动负债计划还款</t>
+          <t>短期借款(revolver)计划还款</t>
         </is>
       </c>
       <c r="B59" s="21" t="inlineStr">
@@ -10137,14 +10137,14 @@
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>分析师修正: 扩产周期存量债务滚动续作(2023-2025年报有息负债余额稳定), 不做计划摊还; 超额现金由FIN页sweep调度</t>
+          <t>通用默认: 短借为revolver, 无计划还款</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>长期借款计划还款</t>
+          <t>一年内到期非流动负债计划还款</t>
         </is>
       </c>
       <c r="B60" s="21" t="inlineStr">
@@ -10169,14 +10169,14 @@
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>分析师修正: 同上, 长期借款滚动续作(强制1/5摊还会使重资产标的FCFE机制性深负, 与公司实际再融资行为不符)</t>
+          <t>分析师修正: 扩产周期存量债务滚动续作(2023-2025年报有息负债余额稳定), 不做计划摊还; 超额现金由FIN页sweep调度</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>租赁负债计划还款</t>
+          <t>长期借款计划还款</t>
         </is>
       </c>
       <c r="B61" s="21" t="inlineStr">
@@ -10201,34 +10201,46 @@
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>分析师修正: 租赁负债滚动续作, 不做计划摊还</t>
+          <t>分析师修正: 同上, 长期借款滚动续作(强制1/5摊还会使重资产标的FCFE机制性深负, 与公司实际再融资行为不符)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>短期借款利率</t>
+          <t>租赁负债计划还款</t>
         </is>
       </c>
       <c r="B62" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C62" s="28" t="n">
-        <v>0.03</v>
+          <t>百万</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="29" t="n">
+        <v>0</v>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 一年期LPR附近</t>
+          <t>分析师修正: 租赁负债滚动续作, 不做计划摊还</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>一年内到期非流动负债利率</t>
+          <t>短期借款利率</t>
         </is>
       </c>
       <c r="B63" s="21" t="inlineStr">
@@ -10237,18 +10249,18 @@
         </is>
       </c>
       <c r="C63" s="28" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 参照综合借款成本</t>
+          <t>通用默认: 一年期LPR附近</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>长期借款利率</t>
+          <t>一年内到期非流动负债利率</t>
         </is>
       </c>
       <c r="B64" s="21" t="inlineStr">
@@ -10257,18 +10269,18 @@
         </is>
       </c>
       <c r="C64" s="28" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 项目贷略高</t>
+          <t>通用默认: 参照综合借款成本</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>租赁负债利率</t>
+          <t>长期借款利率</t>
         </is>
       </c>
       <c r="B65" s="21" t="inlineStr">
@@ -10277,18 +10289,18 @@
         </is>
       </c>
       <c r="C65" s="28" t="n">
-        <v>0.045</v>
+        <v>0.037</v>
       </c>
       <c r="H65" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 租赁内含利率4-5%</t>
+          <t>通用默认: 项目贷略高</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>货币资金收益率(按平均余额)</t>
+          <t>租赁负债利率</t>
         </is>
       </c>
       <c r="B66" s="21" t="inlineStr">
@@ -10297,85 +10309,85 @@
         </is>
       </c>
       <c r="C66" s="28" t="n">
-        <v>0.012</v>
+        <v>0.045</v>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 活期+短期存款1.2%</t>
+          <t>通用默认: 租赁内含利率4-5%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>其他财务费用(手续费/汇兑)</t>
+          <t>货币资金收益率(按平均余额)</t>
         </is>
       </c>
       <c r="B67" s="21" t="inlineStr">
         <is>
-          <t>百万</t>
-        </is>
-      </c>
-      <c r="C67" s="29" t="n">
-        <v>30</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C67" s="28" t="n">
+        <v>0.012</v>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>通用默认: 手续费/汇兑等30百万</t>
+          <t>通用默认: 活期+短期存款1.2%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
+          <t>其他财务费用(手续费/汇兑)</t>
+        </is>
+      </c>
+      <c r="B68" s="21" t="inlineStr">
+        <is>
+          <t>百万</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="n">
+        <v>30</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: 手续费/汇兑等30百万</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
           <t>2025A末有息负债合计</t>
         </is>
       </c>
-      <c r="B68" s="21" t="inlineStr">
+      <c r="B69" s="21" t="inlineStr">
         <is>
           <t>百万</t>
         </is>
       </c>
-      <c r="C68" s="25" t="n">
+      <c r="C69" s="25" t="n">
         <v>12596.2</v>
       </c>
-      <c r="H68" s="11" t="inlineStr">
+      <c r="H69" s="11" t="inlineStr">
         <is>
           <t>＝短借2593.1+一年内7.5+长借9994.8+租赁0.8 (东财F10 2025年报); WACC的Wd市值口径引用本行</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="19" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>十、WACC 与终值 (全公式化, 联动Relative_Val可比beta)</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>无风险利率 rf</t>
-        </is>
-      </c>
-      <c r="B71" s="21" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C71" s="28" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H71" s="9" t="inlineStr">
-        <is>
-          <t>通用默认(港股): 10年期美债收益率约4%(财报币种口径)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>股权风险溢价 ERP</t>
+          <t>无风险利率 rf</t>
         </is>
       </c>
       <c r="B72" s="21" t="inlineStr">
@@ -10384,80 +10396,79 @@
         </is>
       </c>
       <c r="C72" s="28" t="n">
-        <v>0.055</v>
+        <v>0.04</v>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>通用默认: ERP中枢5.5%; 港股口径请按研究修正</t>
+          <t>通用默认(港股): 10年期美债收益率约4%(财报币种口径)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>可比公司无杠杆βu中位数</t>
+          <t>股权风险溢价 ERP</t>
         </is>
       </c>
       <c r="B73" s="21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H73" s="11" t="inlineStr">
-        <is>
-          <t>兜底默认: 未配置可比公司, βu=1.0蓝色输入; 建议补relative_val.comps后自动取中位数</t>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C73" s="28" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H73" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: ERP中枢5.5%; 港股口径请按研究修正</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>目标债务权重 Wd (市值口径)</t>
+          <t>可比公司无杠杆βu中位数</t>
         </is>
       </c>
       <c r="B74" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C74" s="16">
-        <f>C68/(C68+C9)</f>
-        <v/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>1</v>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>＝2025A末有息负债/(有息负债+总市值): 以市值口径现状结构为目标结构</t>
+          <t>兜底默认: 未配置可比公司, βu=1.0蓝色输入; 建议补relative_val.comps后自动取中位数</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>目标 D/E = Wd/(1-Wd)</t>
+          <t>目标债务权重 Wd (市值口径)</t>
         </is>
       </c>
       <c r="B75" s="21" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="C75" s="32">
-        <f>C74/(1-C74)</f>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C75" s="16">
+        <f>C69/(C69+C9)</f>
         <v/>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>relever用目标产权比率</t>
+          <t>＝2025A末有息负债/(有息负债+总市值): 以市值口径现状结构为目标结构</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>再杠杆βl = βu×(1+(1-t)×D/E)</t>
+          <t>目标 D/E = Wd/(1-Wd)</t>
         </is>
       </c>
       <c r="B76" s="21" t="inlineStr">
@@ -10466,39 +10477,40 @@
         </is>
       </c>
       <c r="C76" s="32">
-        <f>C73*(1+(1-C33)*C75)</f>
+        <f>C75/(1-C75)</f>
         <v/>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>Hamada公式, t=2026E有效税率</t>
+          <t>relever用目标产权比率</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>个股/执行风险溢价 (已删除=0)</t>
+          <t>再杠杆βl = βu×(1+(1-t)×D/E)</t>
         </is>
       </c>
       <c r="B77" s="21" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C77" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>通用默认: 不取个股溢价(避免与β/情景重复计价)</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="C77" s="32">
+        <f>C74*(1+(1-C33)*C76)</f>
+        <v/>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>Hamada公式, t=2026E有效税率</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>股权成本 Ke = rf+βl×ERP+溢价</t>
+          <t>个股/执行风险溢价 (已删除=0)</t>
         </is>
       </c>
       <c r="B78" s="21" t="inlineStr">
@@ -10506,20 +10518,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C78" s="16">
-        <f>C71+C76*C72+C77</f>
-        <v/>
-      </c>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>CAPM公式(溢价默认为0)</t>
+      <c r="C78" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: 不取个股溢价(避免与β/情景重复计价)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>债务成本 Kd</t>
+          <t>股权成本 Ke = rf+βl×ERP+溢价</t>
         </is>
       </c>
       <c r="B79" s="21" t="inlineStr">
@@ -10527,19 +10538,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C79" s="28" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="H79" s="9" t="inlineStr">
-        <is>
-          <t>通用默认: ≈债务加权平均利率</t>
+      <c r="C79" s="16">
+        <f>C72+C77*C73+C78</f>
+        <v/>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>CAPM公式(溢价默认为0)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>WACC (计算值)</t>
+          <t>债务成本 Kd</t>
         </is>
       </c>
       <c r="B80" s="21" t="inlineStr">
@@ -10547,20 +10559,19 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C80" s="16">
-        <f>(1-C74)*C78+C74*C79*(1-C33)</f>
-        <v/>
-      </c>
-      <c r="H80" s="11" t="inlineStr">
-        <is>
-          <t>＝(1-Wd)×Ke + Wd×Kd×(1-t)</t>
+      <c r="C80" s="28" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H80" s="9" t="inlineStr">
+        <is>
+          <t>通用默认: ≈债务加权平均利率</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>WACC override (留空=用计算值)</t>
+          <t>WACC (计算值)</t>
         </is>
       </c>
       <c r="B81" s="21" t="inlineStr">
@@ -10568,17 +10579,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C81" s="28" t="n"/>
+      <c r="C81" s="16">
+        <f>(1-C75)*C79+C75*C80*(1-C33)</f>
+        <v/>
+      </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>蓝色输入, 留空则采用上方计算值; 填入数值则覆盖(Checks页校验采用值=计算值或override非空)</t>
+          <t>＝(1-Wd)×Ke + Wd×Kd×(1-t)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>WACC (采用值)</t>
+          <t>WACC override (留空=用计算值)</t>
         </is>
       </c>
       <c r="B82" s="21" t="inlineStr">
@@ -10586,114 +10600,132 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C82" s="18">
-        <f>IF(C81="",C80,C81)</f>
-        <v/>
-      </c>
+      <c r="C82" s="28" t="n"/>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>＝IF(override="", 计算值, override); DCF/Sensitivity/Scenarios全部引用本行</t>
+          <t>蓝色输入, 留空则采用上方计算值; 填入数值则覆盖(Checks页校验采用值=计算值或override非空)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
+          <t>WACC (采用值)</t>
+        </is>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C83" s="18">
+        <f>IF(C82="",C81,C82)</f>
+        <v/>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>＝IF(override="", 计算值, override); DCF/Sensitivity/Scenarios全部引用本行</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
           <t>永续增长率 g</t>
         </is>
       </c>
-      <c r="B83" s="21" t="inlineStr">
+      <c r="B84" s="21" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="C83" s="28" t="n">
+      <c r="C84" s="28" t="n">
         <v>0.03</v>
       </c>
-      <c r="H83" s="9" t="inlineStr">
+      <c r="H84" s="9" t="inlineStr">
         <is>
           <t>通用默认: 长期名义增速中枢下沿</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="19" t="inlineStr">
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>十一、情景参数 (驱动情景开关 &amp; Scenarios页)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>情景</t>
         </is>
       </c>
-      <c r="C86" s="27" t="inlineStr">
+      <c r="C87" s="27" t="inlineStr">
         <is>
           <t>收入增速调整</t>
         </is>
       </c>
-      <c r="D86" s="27" t="inlineStr">
+      <c r="D87" s="27" t="inlineStr">
         <is>
           <t>净利率调整</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>情景逻辑</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="33" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="33" t="inlineStr">
         <is>
           <t>熊市 Bear</t>
         </is>
       </c>
-      <c r="C87" s="28" t="n">
+      <c r="C88" s="28" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D87" s="28" t="n">
+      <c r="D88" s="28" t="n">
         <v>-0.03</v>
       </c>
-      <c r="H87" s="11" t="inlineStr">
+      <c r="H88" s="11" t="inlineStr">
         <is>
           <t>通用默认: 分部增速-15pct, 净利率-3pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>基准 Base</t>
-        </is>
-      </c>
-      <c r="C88" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="11" t="inlineStr">
-        <is>
-          <t>基准: 不调整</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
+          <t>基准 Base</t>
+        </is>
+      </c>
+      <c r="C89" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="11" t="inlineStr">
+        <is>
+          <t>基准: 不调整</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
           <t>牛市 Bull</t>
         </is>
       </c>
-      <c r="C89" s="28" t="n">
+      <c r="C90" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="D89" s="28" t="n">
+      <c r="D90" s="28" t="n">
         <v>0.015</v>
       </c>
-      <c r="H89" s="11" t="inlineStr">
+      <c r="H90" s="11" t="inlineStr">
         <is>
           <t>通用默认: 分部增速+10pct, 净利率+1.5pct</t>
         </is>
@@ -10701,17 +10733,17 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A85:J85"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A53:J53"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A57:J57"/>
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A86:J86"/>
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
@@ -10936,23 +10968,23 @@
         </is>
       </c>
       <c r="E8" s="16">
-        <f>(Assumptions!C$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$87,Assumptions!$C$88,Assumptions!$C$89))</f>
+        <f>(Assumptions!C$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$88,Assumptions!$C$89,Assumptions!$C$90))</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(Assumptions!D$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$87,Assumptions!$C$88,Assumptions!$C$89))</f>
+        <f>(Assumptions!D$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$88,Assumptions!$C$89,Assumptions!$C$90))</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>(Assumptions!E$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$87,Assumptions!$C$88,Assumptions!$C$89))</f>
+        <f>(Assumptions!E$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$88,Assumptions!$C$89,Assumptions!$C$90))</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>(Assumptions!F$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$87,Assumptions!$C$88,Assumptions!$C$89))</f>
+        <f>(Assumptions!F$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$88,Assumptions!$C$89,Assumptions!$C$90))</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>(Assumptions!G$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$87,Assumptions!$C$88,Assumptions!$C$89))</f>
+        <f>(Assumptions!G$21+CHOOSE(Assumptions!$C$5,Assumptions!$C$88,Assumptions!$C$89,Assumptions!$C$90))</f>
         <v/>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -10977,23 +11009,23 @@
         <v>0.2098</v>
       </c>
       <c r="E9" s="16">
-        <f>(Assumptions!C$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$87,Assumptions!$D$88,Assumptions!$D$89))</f>
+        <f>(Assumptions!C$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$88,Assumptions!$D$89,Assumptions!$D$90))</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(Assumptions!D$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$87,Assumptions!$D$88,Assumptions!$D$89))</f>
+        <f>(Assumptions!D$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$88,Assumptions!$D$89,Assumptions!$D$90))</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>(Assumptions!E$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$87,Assumptions!$D$88,Assumptions!$D$89))</f>
+        <f>(Assumptions!E$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$88,Assumptions!$D$89,Assumptions!$D$90))</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>(Assumptions!F$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$87,Assumptions!$D$88,Assumptions!$D$89))</f>
+        <f>(Assumptions!F$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$88,Assumptions!$D$89,Assumptions!$D$90))</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>(Assumptions!G$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$87,Assumptions!$D$88,Assumptions!$D$89))</f>
+        <f>(Assumptions!G$24+CHOOSE(Assumptions!$C$5,Assumptions!$D$88,Assumptions!$D$89,Assumptions!$D$90))</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -11349,7 +11381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -12085,7 +12117,11 @@
         <f>I17-I18</f>
         <v/>
       </c>
-      <c r="J19" s="11" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>合并口径(含少数股东损益)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -12093,171 +12129,212 @@
           <t>归母净利润</t>
         </is>
       </c>
-      <c r="B20" s="36">
-        <f>B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="36">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="36">
-        <f>D19</f>
-        <v/>
+      <c r="B20" s="37" t="n">
+        <v>902.5</v>
+      </c>
+      <c r="C20" s="37" t="n">
+        <v>492.7</v>
+      </c>
+      <c r="D20" s="37" t="n">
+        <v>685.1</v>
       </c>
       <c r="E20" s="36">
-        <f>E19</f>
+        <f>E19*(1-Assumptions!C$34)</f>
         <v/>
       </c>
       <c r="F20" s="36">
-        <f>F19</f>
+        <f>F19*(1-Assumptions!D$34)</f>
         <v/>
       </c>
       <c r="G20" s="36">
-        <f>G19</f>
+        <f>G19*(1-Assumptions!E$34)</f>
         <v/>
       </c>
       <c r="H20" s="36">
-        <f>H19</f>
+        <f>H19*(1-Assumptions!F$34)</f>
         <v/>
       </c>
       <c r="I20" s="36">
-        <f>I19</f>
+        <f>I19*(1-Assumptions!G$34)</f>
         <v/>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>历史: 2023A 9.0亿/2024A 4.9亿/2025A 6.9亿</t>
+          <t>历史: 2023A 9.0亿/2024A 4.9亿/2025A 6.9亿 (config硬数, 归母口径=hist.cf.np); 预测=净利润×(1-少数股东损益占比)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  归母净利率</t>
-        </is>
-      </c>
-      <c r="B21" s="16">
-        <f>B20/B4</f>
-        <v/>
-      </c>
-      <c r="C21" s="16">
-        <f>C20/C4</f>
-        <v/>
-      </c>
-      <c r="D21" s="16">
-        <f>D20/D4</f>
-        <v/>
-      </c>
-      <c r="E21" s="16">
-        <f>E20/E4</f>
-        <v/>
-      </c>
-      <c r="F21" s="16">
-        <f>F20/F4</f>
-        <v/>
-      </c>
-      <c r="G21" s="16">
-        <f>G20/G4</f>
-        <v/>
-      </c>
-      <c r="H21" s="16">
-        <f>H20/H4</f>
-        <v/>
-      </c>
-      <c r="I21" s="16">
-        <f>I20/I4</f>
+          <t>少数股东损益</t>
+        </is>
+      </c>
+      <c r="B21" s="26">
+        <f>B19-B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="26">
+        <f>C19-C20</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>D19-D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="26">
+        <f>E19-E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>F19-F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="26">
+        <f>G19-G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="26">
+        <f>H19-H20</f>
+        <v/>
+      </c>
+      <c r="I21" s="26">
+        <f>I19-I20</f>
         <v/>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>2025A 7.3%</t>
+          <t>＝净利润-归母净利润; 历史为合并与归母口径差(倒挤), 预测=净利润×mi_share</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  归母净利率</t>
+        </is>
+      </c>
+      <c r="B22" s="16">
+        <f>B20/B4</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>C20/C4</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f>D20/D4</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f>E20/E4</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>F20/F4</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>G20/G4</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>H20/H4</f>
+        <v/>
+      </c>
+      <c r="I22" s="16">
+        <f>I20/I4</f>
+        <v/>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>2025A 7.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>EPS(元/股)</t>
         </is>
       </c>
-      <c r="B22" s="14">
+      <c r="B23" s="14">
         <f>B20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="C22" s="14">
+      <c r="C23" s="14">
         <f>C20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D23" s="14">
         <f>D20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E23" s="14">
         <f>E20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="F22" s="14">
+      <c r="F23" s="14">
         <f>F20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G23" s="14">
         <f>G20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="H22" s="14">
+      <c r="H23" s="14">
         <f>H20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="I22" s="14">
+      <c r="I23" s="14">
         <f>I20/Equity_Roll!$C$21</f>
         <v/>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>＝归母/稀释股数(Equity_Roll页, 现=85.61亿股)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>EBIT (利润总额+财务费用)</t>
         </is>
       </c>
-      <c r="B23" s="36">
+      <c r="B24" s="36">
         <f>B17+B13</f>
         <v/>
       </c>
-      <c r="C23" s="36">
+      <c r="C24" s="36">
         <f>C17+C13</f>
         <v/>
       </c>
-      <c r="D23" s="36">
+      <c r="D24" s="36">
         <f>D17+D13</f>
         <v/>
       </c>
-      <c r="E23" s="36">
+      <c r="E24" s="36">
         <f>E17+E13</f>
         <v/>
       </c>
-      <c r="F23" s="36">
+      <c r="F24" s="36">
         <f>F17+F13</f>
         <v/>
       </c>
-      <c r="G23" s="36">
+      <c r="G24" s="36">
         <f>G17+G13</f>
         <v/>
       </c>
-      <c r="H23" s="36">
+      <c r="H24" s="36">
         <f>H17+H13</f>
         <v/>
       </c>
-      <c r="I23" s="36">
+      <c r="I24" s="36">
         <f>I17+I13</f>
         <v/>
       </c>
-      <c r="J23" s="11" t="inlineStr">
+      <c r="J24" s="11" t="inlineStr">
         <is>
           <t>供DCF页FCFF计算</t>
         </is>
@@ -12457,23 +12534,23 @@
         <v>1432.7</v>
       </c>
       <c r="E6" s="26">
-        <f>Assumptions!C$37/365*IS!E4</f>
+        <f>Assumptions!C$38/365*IS!E4</f>
         <v/>
       </c>
       <c r="F6" s="26">
-        <f>Assumptions!D$37/365*IS!F4</f>
+        <f>Assumptions!D$38/365*IS!F4</f>
         <v/>
       </c>
       <c r="G6" s="26">
-        <f>Assumptions!E$37/365*IS!G4</f>
+        <f>Assumptions!E$38/365*IS!G4</f>
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>Assumptions!F$37/365*IS!H4</f>
+        <f>Assumptions!F$38/365*IS!H4</f>
         <v/>
       </c>
       <c r="I6" s="26">
-        <f>Assumptions!G$37/365*IS!I4</f>
+        <f>Assumptions!G$38/365*IS!I4</f>
         <v/>
       </c>
       <c r="J6" s="11" t="inlineStr">
@@ -12498,23 +12575,23 @@
         <v>67.5</v>
       </c>
       <c r="E7" s="26">
-        <f>IS!E4*Assumptions!C$40</f>
+        <f>IS!E4*Assumptions!C$41</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>IS!F4*Assumptions!D$40</f>
+        <f>IS!F4*Assumptions!D$41</f>
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>IS!G4*Assumptions!E$40</f>
+        <f>IS!G4*Assumptions!E$41</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>IS!H4*Assumptions!F$40</f>
+        <f>IS!H4*Assumptions!F$41</f>
         <v/>
       </c>
       <c r="I7" s="26">
-        <f>IS!I4*Assumptions!G$40</f>
+        <f>IS!I4*Assumptions!G$41</f>
         <v/>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -12580,23 +12657,23 @@
         <v>3629.8</v>
       </c>
       <c r="E9" s="26">
-        <f>Assumptions!C$38/365*IS!E6</f>
+        <f>Assumptions!C$39/365*IS!E6</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>Assumptions!D$38/365*IS!F6</f>
+        <f>Assumptions!D$39/365*IS!F6</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>Assumptions!E$38/365*IS!G6</f>
+        <f>Assumptions!E$39/365*IS!G6</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>Assumptions!F$38/365*IS!H6</f>
+        <f>Assumptions!F$39/365*IS!H6</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>Assumptions!G$38/365*IS!I6</f>
+        <f>Assumptions!G$39/365*IS!I6</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -13155,23 +13232,23 @@
         <v>2966</v>
       </c>
       <c r="E23" s="26">
-        <f>Assumptions!C$39/365*IS!E6</f>
+        <f>Assumptions!C$40/365*IS!E6</f>
         <v/>
       </c>
       <c r="F23" s="26">
-        <f>Assumptions!D$39/365*IS!F6</f>
+        <f>Assumptions!D$40/365*IS!F6</f>
         <v/>
       </c>
       <c r="G23" s="26">
-        <f>Assumptions!E$39/365*IS!G6</f>
+        <f>Assumptions!E$40/365*IS!G6</f>
         <v/>
       </c>
       <c r="H23" s="26">
-        <f>Assumptions!F$39/365*IS!H6</f>
+        <f>Assumptions!F$40/365*IS!H6</f>
         <v/>
       </c>
       <c r="I23" s="26">
-        <f>Assumptions!G$39/365*IS!I6</f>
+        <f>Assumptions!G$40/365*IS!I6</f>
         <v/>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -13237,23 +13314,23 @@
         <v>0</v>
       </c>
       <c r="E25" s="26">
-        <f>IS!E4*Assumptions!C$41</f>
+        <f>IS!E4*Assumptions!C$42</f>
         <v/>
       </c>
       <c r="F25" s="26">
-        <f>IS!F4*Assumptions!D$41</f>
+        <f>IS!F4*Assumptions!D$42</f>
         <v/>
       </c>
       <c r="G25" s="26">
-        <f>IS!G4*Assumptions!E$41</f>
+        <f>IS!G4*Assumptions!E$42</f>
         <v/>
       </c>
       <c r="H25" s="26">
-        <f>IS!H4*Assumptions!F$41</f>
+        <f>IS!H4*Assumptions!F$42</f>
         <v/>
       </c>
       <c r="I25" s="26">
-        <f>IS!I4*Assumptions!G$41</f>
+        <f>IS!I4*Assumptions!G$42</f>
         <v/>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -13278,23 +13355,23 @@
         <v>33.5</v>
       </c>
       <c r="E26" s="26">
-        <f>IS!E4*Assumptions!C$42</f>
+        <f>IS!E4*Assumptions!C$43</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>IS!F4*Assumptions!D$42</f>
+        <f>IS!F4*Assumptions!D$43</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>IS!G4*Assumptions!E$42</f>
+        <f>IS!G4*Assumptions!E$43</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>IS!H4*Assumptions!F$42</f>
+        <f>IS!H4*Assumptions!F$43</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>IS!I4*Assumptions!G$42</f>
+        <f>IS!I4*Assumptions!G$43</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -14119,35 +14196,35 @@
           <t>配平差额检查(资产-负债权益)</t>
         </is>
       </c>
-      <c r="B47" s="37">
+      <c r="B47" s="38">
         <f>B21-B46</f>
         <v/>
       </c>
-      <c r="C47" s="37">
+      <c r="C47" s="38">
         <f>C21-C46</f>
         <v/>
       </c>
-      <c r="D47" s="37">
+      <c r="D47" s="38">
         <f>D21-D46</f>
         <v/>
       </c>
-      <c r="E47" s="37">
+      <c r="E47" s="38">
         <f>E21-E46</f>
         <v/>
       </c>
-      <c r="F47" s="37">
+      <c r="F47" s="38">
         <f>F21-F46</f>
         <v/>
       </c>
-      <c r="G47" s="37">
+      <c r="G47" s="38">
         <f>G21-G46</f>
         <v/>
       </c>
-      <c r="H47" s="37">
+      <c r="H47" s="38">
         <f>H21-H46</f>
         <v/>
       </c>
-      <c r="I47" s="37">
+      <c r="I47" s="38">
         <f>I21-I46</f>
         <v/>
       </c>
@@ -14435,13 +14512,13 @@
           <t>经营活动现金流量净额</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n">
+      <c r="B8" s="37" t="n">
         <v>3358.3</v>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="37" t="n">
         <v>3175.6</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="37" t="n">
         <v>3194.3</v>
       </c>
       <c r="E8" s="36">
@@ -14611,13 +14688,13 @@
           <t>投资活动现金流量净额</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n">
+      <c r="B12" s="37" t="n">
         <v>-6207.6</v>
       </c>
-      <c r="C12" s="38" t="n">
+      <c r="C12" s="37" t="n">
         <v>-4518.4</v>
       </c>
-      <c r="D12" s="38" t="n">
+      <c r="D12" s="37" t="n">
         <v>-6495.4</v>
       </c>
       <c r="E12" s="36">
@@ -14793,13 +14870,13 @@
           <t>筹资活动现金流量净额</t>
         </is>
       </c>
-      <c r="B16" s="38" t="n">
+      <c r="B16" s="37" t="n">
         <v>2466.3</v>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C16" s="37" t="n">
         <v>1608.3</v>
       </c>
-      <c r="D16" s="38" t="n">
+      <c r="D16" s="37" t="n">
         <v>2676.5</v>
       </c>
       <c r="E16" s="36">
@@ -14924,13 +15001,13 @@
           <t>期末货币资金(=BS货币资金)</t>
         </is>
       </c>
-      <c r="B19" s="38" t="n">
+      <c r="B19" s="37" t="n">
         <v>6215.1</v>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C19" s="37" t="n">
         <v>6364.2</v>
       </c>
-      <c r="D19" s="38" t="n">
+      <c r="D19" s="37" t="n">
         <v>5872.5</v>
       </c>
       <c r="E19" s="36">
@@ -15660,23 +15737,23 @@
         </is>
       </c>
       <c r="E22" s="26">
-        <f>E21*Assumptions!$C$50</f>
+        <f>E21*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="F22" s="26">
-        <f>F21*Assumptions!$C$50</f>
+        <f>F21*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="G22" s="26">
-        <f>G21*Assumptions!$C$50</f>
+        <f>G21*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="H22" s="26">
-        <f>H21*Assumptions!$C$50</f>
+        <f>H21*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="I22" s="26">
-        <f>I21*Assumptions!$C$50</f>
+        <f>I21*Assumptions!$C$51</f>
         <v/>
       </c>
       <c r="J22" s="11" t="inlineStr">
@@ -15731,23 +15808,23 @@
         </is>
       </c>
       <c r="E26" s="26">
-        <f>IS!D20*Assumptions!C$53</f>
+        <f>IS!D20*Assumptions!C$54</f>
         <v/>
       </c>
       <c r="F26" s="26">
-        <f>IS!E20*Assumptions!D$53</f>
+        <f>IS!E20*Assumptions!D$54</f>
         <v/>
       </c>
       <c r="G26" s="26">
-        <f>IS!F20*Assumptions!E$53</f>
+        <f>IS!F20*Assumptions!E$54</f>
         <v/>
       </c>
       <c r="H26" s="26">
-        <f>IS!G20*Assumptions!F$53</f>
+        <f>IS!G20*Assumptions!F$54</f>
         <v/>
       </c>
       <c r="I26" s="26">
-        <f>IS!H20*Assumptions!G$53</f>
+        <f>IS!H20*Assumptions!G$54</f>
         <v/>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -15900,23 +15977,23 @@
         </is>
       </c>
       <c r="E7" s="26">
-        <f>(E13+E14)*Assumptions!$C$46</f>
+        <f>(E13+E14)*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="F7" s="26">
-        <f>(F13+F14)*Assumptions!$C$46</f>
+        <f>(F13+F14)*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>(G13+G14)*Assumptions!$C$46</f>
+        <f>(G13+G14)*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>(H13+H14)*Assumptions!$C$46</f>
+        <f>(H13+H14)*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="I7" s="26">
-        <f>(I13+I14)*Assumptions!$C$46</f>
+        <f>(I13+I14)*Assumptions!$C$47</f>
         <v/>
       </c>
       <c r="J7" s="11" t="inlineStr">
@@ -15932,23 +16009,23 @@
         </is>
       </c>
       <c r="E8" s="26">
-        <f>E6*Assumptions!$C$47+E7*Assumptions!$C$48</f>
+        <f>E6*Assumptions!$C$48+E7*Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="F8" s="26">
-        <f>F6*Assumptions!$C$47+F7*Assumptions!$C$48</f>
+        <f>F6*Assumptions!$C$48+F7*Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>G6*Assumptions!$C$47+G7*Assumptions!$C$48</f>
+        <f>G6*Assumptions!$C$48+G7*Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>H6*Assumptions!$C$47+H7*Assumptions!$C$48</f>
+        <f>H6*Assumptions!$C$48+H7*Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="I8" s="26">
-        <f>I6*Assumptions!$C$47+I7*Assumptions!$C$48</f>
+        <f>I6*Assumptions!$C$48+I7*Assumptions!$C$49</f>
         <v/>
       </c>
       <c r="J8" s="11" t="inlineStr">
@@ -15964,23 +16041,23 @@
         </is>
       </c>
       <c r="E9" s="26">
-        <f>E6*Assumptions!$C$49</f>
+        <f>E6*Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="F9" s="26">
-        <f>F6*Assumptions!$C$49</f>
+        <f>F6*Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>G6*Assumptions!$C$49</f>
+        <f>G6*Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>H6*Assumptions!$C$49</f>
+        <f>H6*Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="I9" s="26">
-        <f>I6*Assumptions!$C$49</f>
+        <f>I6*Assumptions!$C$50</f>
         <v/>
       </c>
       <c r="J9" s="11" t="inlineStr">
@@ -16066,23 +16143,23 @@
         </is>
       </c>
       <c r="E14" s="26">
-        <f>IS!E4*Assumptions!C$45</f>
+        <f>IS!E4*Assumptions!C$46</f>
         <v/>
       </c>
       <c r="F14" s="26">
-        <f>IS!F4*Assumptions!D$45</f>
+        <f>IS!F4*Assumptions!D$46</f>
         <v/>
       </c>
       <c r="G14" s="26">
-        <f>IS!G4*Assumptions!E$45</f>
+        <f>IS!G4*Assumptions!E$46</f>
         <v/>
       </c>
       <c r="H14" s="26">
-        <f>IS!H4*Assumptions!F$45</f>
+        <f>IS!H4*Assumptions!F$46</f>
         <v/>
       </c>
       <c r="I14" s="26">
-        <f>IS!I4*Assumptions!G$45</f>
+        <f>IS!I4*Assumptions!G$46</f>
         <v/>
       </c>
       <c r="J14" s="11" t="inlineStr">
